--- a/reports/devops-juniors-israel-2026-W27.xlsx
+++ b/reports/devops-juniors-israel-2026-W27.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="391">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-06-29T11:22:14</t>
+    <t xml:space="preserve">2026-06-30T09:58:17</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -163,654 +163,822 @@
     <t xml:space="preserve">2026-06-02</t>
   </si>
   <si>
-    <t xml:space="preserve">AI Inclined Systems Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SB0</t>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calanit by one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Virtualization, Active Directory, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-calanit-by-one-4433302441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
   </si>
   <si>
     <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-inclined-systems-engineer-at-sb0-4429860196</t>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SW DevOps and Test Infrastructure Student, Nitro SW Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon Web Services (AWS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Terraform/IaC, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sw-devops-and-test-infrastructure-student-nitro-sw-team-at-amazon-web-services-aws-4432816876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC &amp; SOC Analyst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-soc-analyst-at-commit-4421804878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-ai-4430612805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-4433428247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peak Innovation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, Cloud (any), Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-peak-innovation-4431041046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experienced IT System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iFOR FINTECH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/experienced-it-system-administrator-at-ifor-fintech-4428923734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator – Advanced Data Center and AI Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-ai-4427315937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator &amp; IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inManage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Corp System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payoneer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.payoneer.com/careers/position/7916835/?gh_jid=7916835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Infrastructure &amp; Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Squadron Israel - Hatayeset</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Cloud (any), Git, Terraform/IaC, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infrastructure-technical-support-specialist-at-the-squadron-israel-hatayeset-4421938671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Operations Student - Nights &amp; Weekend shifts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voyantis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Git, Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-operations-student-nights-weekend-shifts-at-voyantis-4422723294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shavit Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Kubernetes, Networking, Monitoring, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-shavit-software-4426784526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-at-paragon-4417886377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer - Intern position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Align Technology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Cloud (any), Monitoring, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-intern-position-at-align-technology-4303646784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashdod, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Kubernetes, Networking, Virtualization, Active Directory, Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-sqlink-group-4432227642</t>
   </si>
   <si>
     <t xml:space="preserve">2026-06-24</t>
   </si>
   <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-4433428247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-ai-4430612805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anecdotes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-anecdotes-4429933095</t>
+    <t xml:space="preserve">Help Desk and System Administrator (Israel)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Terraform/IaC, Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-and-system-administrator-israel-at-zota-4431223683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MyHeritage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-myheritage-4434704007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Droxi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-operations-engineer-at-droxi-4426788584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Menora Mivtachim Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-menora-mivtachim-group-4434972024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Help Desk (student position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LiveU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-student-position-at-liveu-4434277505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spinomenal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-spinomenal-4431228721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Innoviz Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-innoviz-technologies-4407119527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Korentec Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-yael-korentec-technologies-4431373486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4430443104</t>
   </si>
   <si>
     <t xml:space="preserve">2026-06-18</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IOT student tester</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Motorola Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/iot-student-tester-at-motorola-solutions-4434451222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Corp System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Payoneer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.payoneer.com/careers/position/7916835/?gh_jid=7916835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashdod, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Kubernetes, Networking, Virtualization, Active Directory, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-sqlink-group-4432227642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compie Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, Cloud (any), Networking, Virtualization, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-compie-technologies-4434281959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk and System Administrator (Israel)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Terraform/IaC, Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-and-system-administrator-israel-at-zota-4431223683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Droxi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-operations-engineer-at-droxi-4426788584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Help Desk (student position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LiveU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-student-position-at-liveu-4434277505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4430443104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Desktop Support Engineer (Freelance / Backfill)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allied Worldwide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-freelance-backfill-at-allied-worldwide-4423894444</t>
+    <t xml:space="preserve">IT Desktop Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zensar Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-at-zensar-technologies-4418821535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator - JB-651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PwC Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system%C2%A0administrator-jb-651-at-pwc-israel-4429917341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Service Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer (35684)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-35684-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4434276396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMAREL LTD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-amarel-ltd-4428035454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk (24892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-24892-at-yael-group-4427354216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Network Operations Center Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tata Consultancy Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-operations-center-operator-at-tata-consultancy-services-4413535925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Bootcamp Course</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-at-abra-4432200564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4406043821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plarium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-administrator-at-plarium-4431096159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">טכנאי/ת Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4427161897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-tata-consultancy-services-4430592021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Specialist - JB-594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-jb-594-at-pwc-israel-4429922813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk (Temporary)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personetics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-temporary-at-personetics-4428653392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">איש/אשת Help Desk Tier 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Webox LTD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%90%D7%99%D7%A9-%D7%90%D7%A9%D7%AA-help-desk-tier-1-at-webox-ltd-4430232360</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ONE Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-one-technologies-4432205195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Support Representative</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weizmann Institute of Science</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-representative-at-weizmann-institute-of-science-4431080100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer- Student Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global-e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-student-position-at-global-e-4378147513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft System Administrator (36014)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-administrator-36014-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4434285138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4425017778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wobi Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-junior-at-wobi-ltd-4419670684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician (Part-Time)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential Careers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-part-time-at-confidential-careers-4425768937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-sqlink-group-4429856103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AudioCodes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4395665709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WSC Sports</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-wsc-sports-4415703367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-abra-4423876931</t>
   </si>
   <si>
     <t xml:space="preserve">2026-06-03</t>
   </si>
   <si>
-    <t xml:space="preserve">AI Bootcamp Course 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Git</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-2-at-abra-4383549364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator - JB-651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PwC Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system%C2%A0administrator-jb-651-at-pwc-israel-4429917341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Service Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer (35684)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-35684-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4434276396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk (24892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-24892-at-yael-group-4427354216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4405545785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tata Consultancy Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-tata-consultancy-services-4430592021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Specialist - JB-594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-jb-594-at-pwc-israel-4429922813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk (Temporary)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Personetics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-temporary-at-personetics-4428653392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">איש/אשת Help Desk Tier 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Webox LTD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%90%D7%99%D7%A9-%D7%90%D7%A9%D7%AA-help-desk-tier-1-at-webox-ltd-4430232360</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ONE Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-one-technologies-4432205195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Support Representative</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weizmann Institute of Science</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-representative-at-weizmann-institute-of-science-4431080100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bright Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-at-bright-data-4419013320</t>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zoho</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-zoho-4427961067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multimedia Systems &amp; IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deloitte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/multimedia-systems-it-support-specialist-at-deloitte-4433302126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist (Part time )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvei</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-part-time-at-nuvei-4421067573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Operations Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unity3D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://unity.com/careers/positions/7860478?gh_jid=7860478</t>
   </si>
   <si>
     <t xml:space="preserve">2026-05-28</t>
   </si>
   <si>
-    <t xml:space="preserve">RealPlay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SpotNet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shoham, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-spotnet-4433071607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft System Administrator (36014)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-administrator-36014-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4434285138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator – WMS | עולם הלוגיסטיקה</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beth-El Industries Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zikhron Yaakov, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-wms-%D7%A2%D7%95%D7%9C%D7%9D-%D7%94%D7%9C%D7%95%D7%92%D7%99%D7%A1%D7%98%D7%99%D7%A7%D7%94-at-beth-el-industries-ltd-4353742304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4425017778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wobi Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-junior-at-wobi-ltd-4419670684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician (Part-Time)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential Careers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-part-time-at-confidential-careers-4425768937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician - junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mornex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-junior-at-mornex-4416807351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-sqlink-group-4429856103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AudioCodes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4395665709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WSC Sports</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-wsc-sports-4415703367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zoho</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-zoho-4427961067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Multimedia Systems &amp; IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deloitte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/multimedia-systems-it-support-specialist-at-deloitte-4433302126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist (Part time )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvei</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-part-time-at-nuvei-4421067573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Operations Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unity3D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://unity.com/careers/positions/7860478?gh_jid=7860478</t>
-  </si>
-  <si>
     <t xml:space="preserve">NOC Analyst (Student Position)</t>
   </si>
   <si>
@@ -856,112 +1024,112 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-28516-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4434281333</t>
   </si>
   <si>
-    <t xml:space="preserve">Information Technology Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NeoTech Israel | ניאוטק ישראל</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-help-desk-at-neotech-israel-%D7%A0%D7%99%D7%90%D7%95%D7%98%D7%A7-%D7%99%D7%A9%D7%A8%D7%90%D7%9C-4414860456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">טכנאי/ת Help desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genie</t>
+    <t xml:space="preserve">Service Desk Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-desk-operator-at-tata-consultancy-services-4427424594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">תומך/ת Help Desk וטכנאי/ת PC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accel Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%AA%D7%95%D7%9E%D7%9A-%D7%AA-help-desk%C2%A0%D7%95%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-pc-at-accel-solutions-4431094783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oktopost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-oktopost-4431366669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Customer Support Helpdesk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Empathy Talent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">California, California, United States</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-customer-support-helpdesk-specialist-empathy-talent-1134244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Customer Support Technician Helpdesk Offboardings &amp;amp; Access</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pixel Machinery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-customer-support-technician-helpdesk-offboardings-amp-access-pixel-machinery-1134154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scheduling Coordinator Entry Level No Experience Needed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Travel Planning Professionals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New York, New York, United States</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-scheduling-coordinator-entry-level-no-experience-needed-travel-planning-professionals-1134108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roles requiring it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What to learn / where to start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
   </si>
   <si>
     <t xml:space="preserve">Virtualization</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4410001855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oktopost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-oktopost-4431366669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Customer Support Technician Helpdesk Offboardings &amp;amp; Access</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pixel Machinery</t>
-  </si>
-  <si>
-    <t xml:space="preserve">California, California, United States</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-customer-support-technician-helpdesk-offboardings-amp-access-pixel-machinery-1134154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medical System Implementor Student (Part-Time, Temporary)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shavit Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/medical-system-implementor-student-part-time-temporary-at-shavit-software-4433076878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scheduling Coordinator Entry Level No Experience Needed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Travel Planning Professionals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New York, New York, United States</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-scheduling-coordinator-entry-level-no-experience-needed-travel-planning-professionals-1134108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roles requiring it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What to learn / where to start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
+    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
   </si>
   <si>
     <t xml:space="preserve">Azure</t>
@@ -970,28 +1138,25 @@
     <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
   </si>
   <si>
-    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pro Git book (free online) + create a learning repo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
   </si>
   <si>
     <t xml:space="preserve">CI/CD</t>
   </si>
   <si>
     <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google Cloud Skills Boost (free) → ACE cert</t>
   </si>
   <si>
     <t xml:space="preserve">Count</t>
@@ -1146,7 +1311,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>58</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7">
@@ -1154,7 +1319,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
@@ -1162,7 +1327,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9">
@@ -1170,7 +1335,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>346</v>
+        <v>361</v>
       </c>
     </row>
     <row r="10">
@@ -1252,7 +1417,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="22">
@@ -1260,7 +1425,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>15</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23">
@@ -1294,7 +1459,7 @@
         <v>30</v>
       </c>
       <c r="B27" s="3">
-        <v>49</v>
+        <v>63</v>
       </c>
     </row>
     <row r="28">
@@ -1310,7 +1475,7 @@
         <v>32</v>
       </c>
       <c r="B29" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -1322,8 +1487,8 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="34" customWidth="1"/>
-    <col min="4" max="4" width="42" customWidth="1"/>
+    <col min="3" max="3" width="33" customWidth="1"/>
+    <col min="4" max="4" width="43" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
     <col min="7" max="7" width="60" customWidth="1"/>
@@ -1407,25 +1572,25 @@
         <v>50</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F3" s="3">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I3" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="H3" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>53</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="4">
@@ -1433,31 +1598,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>56</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>57</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F4" s="3">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="5">
@@ -1465,7 +1630,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>61</v>
@@ -1477,19 +1642,19 @@
         <v>26</v>
       </c>
       <c r="F5" s="3">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6">
@@ -1497,31 +1662,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F6" s="3">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7">
@@ -1529,31 +1694,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F7" s="3">
-        <v>57</v>
+        <v>84</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8">
@@ -1561,31 +1726,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>51</v>
+        <v>78</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F8" s="3">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9">
@@ -1593,31 +1758,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="C9" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" s="3">
+        <v>76</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F9" s="3">
-        <v>47</v>
-      </c>
-      <c r="G9" s="3" t="s">
+      <c r="H9" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="J9" s="3" t="s">
         <v>81</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="10">
@@ -1625,31 +1790,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F10" s="3">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="11">
@@ -1657,31 +1822,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F11" s="3">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12">
@@ -1689,19 +1854,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F12" s="3">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>96</v>
@@ -1713,7 +1878,7 @@
         <v>97</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13">
@@ -1721,31 +1886,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>55</v>
+        <v>98</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F13" s="3">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="G13" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="H13" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I13" s="3" t="s">
+      <c r="J13" s="3" t="s">
         <v>101</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="14">
@@ -1759,13 +1924,13 @@
         <v>103</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F14" s="3">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>104</v>
@@ -1777,7 +1942,7 @@
         <v>105</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15">
@@ -1794,22 +1959,22 @@
         <v>108</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F15" s="3">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>109</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>110</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
     </row>
     <row r="16">
@@ -1817,31 +1982,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F16" s="3">
+        <v>44</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="H16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="E16" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F16" s="3">
-        <v>30</v>
-      </c>
-      <c r="G16" s="3" t="s">
+      <c r="J16" s="3" t="s">
         <v>115</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="17">
@@ -1849,19 +2014,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="D17" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>99</v>
-      </c>
       <c r="E17" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F17" s="3">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>119</v>
@@ -1887,13 +2052,13 @@
         <v>123</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F18" s="3">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>124</v>
@@ -1905,7 +2070,7 @@
         <v>125</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19">
@@ -1919,25 +2084,25 @@
         <v>127</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>90</v>
+        <v>128</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F19" s="3">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>130</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20">
@@ -1948,28 +2113,28 @@
         <v>131</v>
       </c>
       <c r="C20" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F20" s="3">
+        <v>44</v>
+      </c>
+      <c r="G20" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F20" s="3">
-        <v>26</v>
-      </c>
-      <c r="G20" s="3" t="s">
+      <c r="H20" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>134</v>
-      </c>
       <c r="J20" s="3" t="s">
-        <v>73</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21">
@@ -1977,31 +2142,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>136</v>
-      </c>
       <c r="D21" s="3" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F21" s="3">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="G21" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I21" s="3" t="s">
+      <c r="J21" s="3" t="s">
         <v>138</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="22">
@@ -2009,31 +2174,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>132</v>
-      </c>
       <c r="D22" s="3" t="s">
-        <v>99</v>
+        <v>140</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F22" s="3">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>73</v>
+        <v>143</v>
       </c>
     </row>
     <row r="23">
@@ -2041,31 +2206,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>144</v>
+        <v>62</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F23" s="3">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>73</v>
+        <v>143</v>
       </c>
     </row>
     <row r="24">
@@ -2073,31 +2238,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>99</v>
+        <v>150</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F24" s="3">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25">
@@ -2105,31 +2270,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>114</v>
+        <v>155</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F25" s="3">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>68</v>
+        <v>121</v>
       </c>
     </row>
     <row r="26">
@@ -2137,31 +2302,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>155</v>
+        <v>76</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>157</v>
+        <v>128</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F26" s="3">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>160</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -2201,7 +2366,7 @@
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="42" customWidth="1"/>
+    <col min="3" max="3" width="44" customWidth="1"/>
     <col min="4" max="4" width="31" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -2279,7 +2444,7 @@
         <v>48</v>
       </c>
       <c r="K2" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3">
@@ -2290,71 +2455,71 @@
         <v>50</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E3" s="3">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="F3" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I3" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="J3" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="K3" s="3">
-        <v>5</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>56</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>57</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E4" s="3">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="F4" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="J4" s="3" t="s">
-        <v>60</v>
-      </c>
       <c r="K4" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>61</v>
@@ -2366,10 +2531,10 @@
         <v>26</v>
       </c>
       <c r="E5" s="3">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>166</v>
@@ -2378,33 +2543,33 @@
         <v>30</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="K5" s="3">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E6" s="3">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>166</v>
@@ -2413,33 +2578,33 @@
         <v>30</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="K6" s="3">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E7" s="3">
-        <v>57</v>
+        <v>84</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>166</v>
@@ -2448,33 +2613,33 @@
         <v>30</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="K7" s="3">
-        <v>45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>51</v>
+        <v>78</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E8" s="3">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>166</v>
@@ -2483,103 +2648,103 @@
         <v>30</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="K8" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="3">
+        <v>76</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" s="3">
-        <v>47</v>
-      </c>
-      <c r="F9" s="3" t="s">
+      <c r="G9" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="J9" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>73</v>
-      </c>
       <c r="K9" s="3">
-        <v>45</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E10" s="3">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>166</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="K10" s="3">
-        <v>41</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E11" s="3">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>166</v>
@@ -2588,30 +2753,30 @@
         <v>30</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="K11" s="3">
-        <v>45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E12" s="3">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>96</v>
@@ -2626,45 +2791,45 @@
         <v>97</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="K12" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>55</v>
+        <v>98</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E13" s="3">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="F13" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="G13" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I13" s="3" t="s">
+      <c r="J13" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="J13" s="3" t="s">
-        <v>78</v>
-      </c>
       <c r="K13" s="3">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14">
@@ -2675,13 +2840,13 @@
         <v>103</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E14" s="3">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>104</v>
@@ -2696,10 +2861,10 @@
         <v>105</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="K14" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -2713,10 +2878,10 @@
         <v>108</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E15" s="3">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>109</v>
@@ -2725,68 +2890,68 @@
         <v>166</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>110</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
       <c r="K15" s="3">
-        <v>18</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="C16" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" s="3">
+        <v>44</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="G16" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E16" s="3">
-        <v>30</v>
-      </c>
-      <c r="F16" s="3" t="s">
+      <c r="J16" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="G16" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>78</v>
-      </c>
       <c r="K16" s="3">
-        <v>0</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="C17" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>99</v>
-      </c>
       <c r="D17" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E17" s="3">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>119</v>
@@ -2804,7 +2969,7 @@
         <v>121</v>
       </c>
       <c r="K17" s="3">
-        <v>40</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18">
@@ -2815,13 +2980,13 @@
         <v>123</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E18" s="3">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>124</v>
@@ -2836,10 +3001,10 @@
         <v>125</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="K18" s="3">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2850,16 +3015,16 @@
         <v>127</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>90</v>
+        <v>128</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E19" s="3">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>166</v>
@@ -2868,13 +3033,13 @@
         <v>30</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>130</v>
+        <v>59</v>
       </c>
       <c r="K19" s="3">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2882,89 +3047,89 @@
         <v>131</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E20" s="3">
+        <v>44</v>
+      </c>
+      <c r="F20" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E20" s="3">
-        <v>26</v>
-      </c>
-      <c r="F20" s="3" t="s">
+      <c r="G20" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>134</v>
-      </c>
       <c r="J20" s="3" t="s">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="K20" s="3">
-        <v>45</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>136</v>
-      </c>
       <c r="C21" s="3" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E21" s="3">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="F21" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I21" s="3" t="s">
+      <c r="J21" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>68</v>
-      </c>
       <c r="K21" s="3">
-        <v>11</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>132</v>
-      </c>
       <c r="C22" s="3" t="s">
-        <v>99</v>
+        <v>140</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E22" s="3">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>166</v>
@@ -2973,68 +3138,68 @@
         <v>30</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>73</v>
+        <v>143</v>
       </c>
       <c r="K22" s="3">
-        <v>45</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>144</v>
+        <v>62</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E23" s="3">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>166</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>73</v>
+        <v>143</v>
       </c>
       <c r="K23" s="3">
-        <v>45</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>99</v>
+        <v>150</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E24" s="3">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>166</v>
@@ -3043,33 +3208,33 @@
         <v>30</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K24" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>114</v>
+        <v>155</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E25" s="3">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>166</v>
@@ -3078,33 +3243,33 @@
         <v>30</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>68</v>
+        <v>121</v>
       </c>
       <c r="K25" s="3">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>155</v>
+        <v>76</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>157</v>
+        <v>128</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E26" s="3">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>166</v>
@@ -3113,13 +3278,13 @@
         <v>30</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>160</v>
+        <v>59</v>
       </c>
       <c r="K26" s="3">
-        <v>35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -3136,7 +3301,7 @@
         <v>25</v>
       </c>
       <c r="E27" s="3">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>170</v>
@@ -3145,7 +3310,7 @@
         <v>166</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>171</v>
@@ -3154,7 +3319,7 @@
         <v>172</v>
       </c>
       <c r="K27" s="3">
-        <v>36</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -3165,16 +3330,16 @@
         <v>174</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>51</v>
+        <v>175</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E28" s="3">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>166</v>
@@ -3183,10 +3348,10 @@
         <v>30</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>177</v>
+        <v>143</v>
       </c>
       <c r="K28" s="3">
         <v>6</v>
@@ -3194,22 +3359,22 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B29" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>136</v>
-      </c>
       <c r="C29" s="3" t="s">
-        <v>51</v>
+        <v>179</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E29" s="3">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>166</v>
@@ -3218,33 +3383,33 @@
         <v>30</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>68</v>
+        <v>182</v>
       </c>
       <c r="K29" s="3">
-        <v>11</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>182</v>
+        <v>91</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E30" s="3">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>166</v>
@@ -3253,68 +3418,68 @@
         <v>30</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>185</v>
+        <v>138</v>
       </c>
       <c r="K30" s="3">
-        <v>14</v>
+        <v>41</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>186</v>
+        <v>49</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>187</v>
       </c>
       <c r="C31" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E31" s="3">
+        <v>28</v>
+      </c>
+      <c r="F31" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="D31" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E31" s="3">
-        <v>10</v>
-      </c>
-      <c r="F31" s="3" t="s">
+      <c r="G31" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I31" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="G31" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I31" s="3" t="s">
+      <c r="J31" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="J31" s="3" t="s">
-        <v>191</v>
-      </c>
       <c r="K31" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="B32" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>193</v>
-      </c>
       <c r="C32" s="3" t="s">
-        <v>194</v>
+        <v>62</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E32" s="3">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>166</v>
@@ -3323,13 +3488,13 @@
         <v>30</v>
       </c>
       <c r="I32" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="J32" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>177</v>
-      </c>
       <c r="K32" s="3">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="33">
@@ -3346,7 +3511,7 @@
         <v>25</v>
       </c>
       <c r="E33" s="3">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>199</v>
@@ -3361,115 +3526,115 @@
         <v>200</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>78</v>
+        <v>182</v>
       </c>
       <c r="K33" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="C34" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E34" s="3">
+        <v>24</v>
+      </c>
+      <c r="F34" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="G34" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I34" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="D34" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E34" s="3">
-        <v>10</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>205</v>
-      </c>
       <c r="J34" s="3" t="s">
-        <v>206</v>
+        <v>89</v>
       </c>
       <c r="K34" s="3">
-        <v>32</v>
+        <v>46</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>64</v>
+        <v>204</v>
       </c>
       <c r="B35" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E35" s="3">
+        <v>24</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I35" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="C35" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E35" s="3">
-        <v>10</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>208</v>
-      </c>
       <c r="J35" s="3" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="K35" s="3">
-        <v>36</v>
+        <v>12</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="C36" s="3" t="s">
         <v>210</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>211</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E36" s="3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>183</v>
+        <v>211</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>166</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I36" s="3" t="s">
         <v>212</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>191</v>
+        <v>89</v>
       </c>
       <c r="K36" s="3">
-        <v>3</v>
+        <v>46</v>
       </c>
     </row>
     <row r="37">
@@ -3477,19 +3642,19 @@
         <v>213</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>148</v>
+        <v>214</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E37" s="3">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>166</v>
@@ -3498,33 +3663,33 @@
         <v>30</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="K37" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>216</v>
+        <v>76</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>217</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>218</v>
+        <v>56</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E38" s="3">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>166</v>
@@ -3533,118 +3698,118 @@
         <v>30</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>172</v>
+        <v>101</v>
       </c>
       <c r="K38" s="3">
-        <v>36</v>
+        <v>13</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>132</v>
+        <v>220</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>99</v>
+        <v>169</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E39" s="3">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="F39" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I39" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="G39" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H39" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I39" s="3" t="s">
-        <v>223</v>
-      </c>
       <c r="J39" s="3" t="s">
-        <v>224</v>
+        <v>195</v>
       </c>
       <c r="K39" s="3">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="C40" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="D40" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E40" s="3">
+        <v>16</v>
+      </c>
+      <c r="F40" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="C40" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E40" s="3">
-        <v>6</v>
-      </c>
-      <c r="F40" s="3" t="s">
+      <c r="G40" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I40" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="G40" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I40" s="3" t="s">
-        <v>228</v>
-      </c>
       <c r="J40" s="3" t="s">
-        <v>229</v>
+        <v>59</v>
       </c>
       <c r="K40" s="3">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E41" s="3">
+        <v>13</v>
+      </c>
+      <c r="F41" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="G41" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I41" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="C41" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E41" s="3">
-        <v>6</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I41" s="3" t="s">
+      <c r="J41" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>185</v>
-      </c>
       <c r="K41" s="3">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42">
@@ -3658,10 +3823,10 @@
         <v>235</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E42" s="3">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>236</v>
@@ -3676,27 +3841,27 @@
         <v>237</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>238</v>
+        <v>53</v>
       </c>
       <c r="K42" s="3">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>173</v>
+        <v>238</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>94</v>
+        <v>239</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>239</v>
+        <v>45</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E43" s="3">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>240</v>
@@ -3711,30 +3876,30 @@
         <v>241</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="K43" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>192</v>
+        <v>242</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>239</v>
+        <v>140</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E44" s="3">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>222</v>
+        <v>244</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>166</v>
@@ -3743,68 +3908,68 @@
         <v>30</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>172</v>
+        <v>121</v>
       </c>
       <c r="K44" s="3">
-        <v>36</v>
+        <v>19</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>108</v>
+        <v>248</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E45" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>166</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>247</v>
+        <v>53</v>
       </c>
       <c r="K45" s="3">
-        <v>29</v>
+        <v>37</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>248</v>
+        <v>148</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>249</v>
+        <v>224</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E46" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>166</v>
@@ -3813,13 +3978,13 @@
         <v>30</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>252</v>
+        <v>232</v>
       </c>
       <c r="K46" s="3">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47">
@@ -3827,19 +3992,19 @@
         <v>253</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E47" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>219</v>
+        <v>251</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>166</v>
@@ -3848,33 +4013,33 @@
         <v>30</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>60</v>
+        <v>195</v>
       </c>
       <c r="K47" s="3">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="B48" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="C48" s="3" t="s">
         <v>257</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>51</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E48" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>222</v>
+        <v>258</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>166</v>
@@ -3883,30 +4048,30 @@
         <v>30</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K48" s="3">
-        <v>31</v>
+        <v>15</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>262</v>
+        <v>175</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E49" s="3">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>263</v>
@@ -3915,36 +4080,36 @@
         <v>166</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I49" s="3" t="s">
         <v>264</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>206</v>
+        <v>265</v>
       </c>
       <c r="K49" s="3">
-        <v>32</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E50" s="3">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>166</v>
@@ -3956,42 +4121,42 @@
         <v>268</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>269</v>
+        <v>232</v>
       </c>
       <c r="K50" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="B51" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="B51" s="3" t="s">
+      <c r="C51" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="C51" s="3" t="s">
+      <c r="D51" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E51" s="3">
+        <v>10</v>
+      </c>
+      <c r="F51" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="D51" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E51" s="3">
-        <v>4</v>
-      </c>
-      <c r="F51" s="3" t="s">
+      <c r="G51" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I51" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="G51" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H51" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I51" s="3" t="s">
-        <v>274</v>
-      </c>
       <c r="J51" s="3" t="s">
-        <v>60</v>
+        <v>172</v>
       </c>
       <c r="K51" s="3">
         <v>1</v>
@@ -3999,57 +4164,57 @@
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="B52" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="B52" s="3" t="s">
-        <v>261</v>
-      </c>
       <c r="C52" s="3" t="s">
-        <v>262</v>
+        <v>73</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E52" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>263</v>
+        <v>276</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>166</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>172</v>
+        <v>59</v>
       </c>
       <c r="K52" s="3">
-        <v>36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>148</v>
+        <v>214</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E53" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>166</v>
@@ -4058,33 +4223,33 @@
         <v>30</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="K53" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>281</v>
+        <v>201</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E54" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="G54" s="3" t="s">
         <v>166</v>
@@ -4093,33 +4258,33 @@
         <v>30</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>160</v>
+        <v>284</v>
       </c>
       <c r="K54" s="3">
-        <v>35</v>
+        <v>22</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>194</v>
+        <v>175</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E55" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="G55" s="3" t="s">
         <v>166</v>
@@ -4128,33 +4293,33 @@
         <v>30</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="K55" s="3">
-        <v>34</v>
+        <v>9</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>209</v>
+        <v>290</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E56" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>263</v>
+        <v>287</v>
       </c>
       <c r="G56" s="3" t="s">
         <v>166</v>
@@ -4163,67 +4328,69 @@
         <v>30</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>54</v>
+        <v>260</v>
       </c>
       <c r="K56" s="3">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>290</v>
+        <v>148</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>291</v>
+        <v>139</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>292</v>
+        <v>150</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E57" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>263</v>
+        <v>293</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>166</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>60</v>
+        <v>143</v>
       </c>
       <c r="K57" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>294</v>
+        <v>266</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>295</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
-      </c>
-      <c r="F58" s="3"/>
+        <v>6</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>282</v>
+      </c>
       <c r="G58" s="3" t="s">
         <v>166</v>
       </c>
@@ -4234,10 +4401,10 @@
         <v>296</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="K58" s="3">
-        <v>0</v>
+        <v>37</v>
       </c>
     </row>
     <row r="59">
@@ -4248,33 +4415,558 @@
         <v>298</v>
       </c>
       <c r="C59" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E59" s="3">
+        <v>6</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I59" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="D59" s="3" t="s">
+      <c r="J59" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="K59" s="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E60" s="3">
+        <v>6</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="K60" s="3">
         <v>27</v>
       </c>
-      <c r="E59" s="3">
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E61" s="3">
+        <v>6</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I61" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="J61" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="K61" s="3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E62" s="3">
+        <v>6</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="K62" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E63" s="3">
+        <v>6</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I63" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="J63" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="K63" s="3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E64" s="3">
+        <v>4</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I64" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="J64" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="K64" s="3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E65" s="3">
+        <v>4</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I65" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="J65" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="K65" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E66" s="3">
+        <v>4</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="K66" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E67" s="3">
+        <v>3</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I67" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="J67" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="K67" s="3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E68" s="3">
+        <v>3</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I68" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="J68" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="K68" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E69" s="3">
+        <v>3</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I69" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="J69" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="K69" s="3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E70" s="3">
+        <v>3</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I70" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="J70" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="K70" s="3">
         <v>0</v>
       </c>
-      <c r="F59" s="3"/>
-      <c r="G59" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H59" s="3" t="s">
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E71" s="3">
+        <v>3</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I71" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="J71" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="K71" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E72" s="3">
+        <v>3</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H72" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="K59" s="3">
-        <v>1</v>
+      <c r="I72" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="K72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E73" s="3">
+        <v>3</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H73" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I73" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="J73" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="K73" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E74" s="3">
+        <v>0</v>
+      </c>
+      <c r="F74" s="3"/>
+      <c r="G74" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I74" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="J74" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="K74" s="3">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K59"/>
+  <autoFilter ref="A1:K74"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -4334,6 +5026,21 @@
     <hyperlink ref="I57" r:id="rId56"/>
     <hyperlink ref="I58" r:id="rId57"/>
     <hyperlink ref="I59" r:id="rId58"/>
+    <hyperlink ref="I60" r:id="rId59"/>
+    <hyperlink ref="I61" r:id="rId60"/>
+    <hyperlink ref="I62" r:id="rId61"/>
+    <hyperlink ref="I63" r:id="rId62"/>
+    <hyperlink ref="I64" r:id="rId63"/>
+    <hyperlink ref="I65" r:id="rId64"/>
+    <hyperlink ref="I66" r:id="rId65"/>
+    <hyperlink ref="I67" r:id="rId66"/>
+    <hyperlink ref="I68" r:id="rId67"/>
+    <hyperlink ref="I69" r:id="rId68"/>
+    <hyperlink ref="I70" r:id="rId69"/>
+    <hyperlink ref="I71" r:id="rId70"/>
+    <hyperlink ref="I72" r:id="rId71"/>
+    <hyperlink ref="I73" r:id="rId72"/>
+    <hyperlink ref="I74" r:id="rId73"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4341,8 +5048,8 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="59" customWidth="1"/>
-    <col min="2" max="2" width="31" customWidth="1"/>
+    <col min="1" max="1" width="58" customWidth="1"/>
+    <col min="2" max="2" width="27" customWidth="1"/>
     <col min="3" max="3" width="25" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
@@ -4375,125 +5082,367 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D2" s="3">
-        <v>52</v>
+        <v>100</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D3" s="3">
-        <v>40</v>
+        <v>92</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>101</v>
+        <v>70</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>112</v>
+        <v>71</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>113</v>
+        <v>72</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D4" s="3">
-        <v>30</v>
+        <v>84</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>115</v>
+        <v>74</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>116</v>
+        <v>75</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>196</v>
+        <v>76</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>197</v>
+        <v>90</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D5" s="3">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>199</v>
+        <v>92</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>200</v>
+        <v>93</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>294</v>
+        <v>94</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>295</v>
+        <v>95</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="3">
+        <v>52</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="3">
+        <v>52</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="3">
-        <v>0</v>
-      </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>78</v>
+      <c r="D8" s="3">
+        <v>44</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="3">
+        <v>44</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="3">
+        <v>34</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="3">
+        <v>32</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" s="3">
+        <v>16</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D13" s="3">
+        <v>13</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D14" s="3">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" s="3">
+        <v>3</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D16" s="3">
+        <v>3</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G6"/>
+  <autoFilter ref="A1:G16"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
     <hyperlink ref="F4" r:id="rId3"/>
     <hyperlink ref="F5" r:id="rId4"/>
     <hyperlink ref="F6" r:id="rId5"/>
+    <hyperlink ref="F7" r:id="rId6"/>
+    <hyperlink ref="F8" r:id="rId7"/>
+    <hyperlink ref="F9" r:id="rId8"/>
+    <hyperlink ref="F10" r:id="rId9"/>
+    <hyperlink ref="F11" r:id="rId10"/>
+    <hyperlink ref="F12" r:id="rId11"/>
+    <hyperlink ref="F13" r:id="rId12"/>
+    <hyperlink ref="F14" r:id="rId13"/>
+    <hyperlink ref="F15" r:id="rId14"/>
+    <hyperlink ref="F16" r:id="rId15"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4508,178 +5457,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>301</v>
+        <v>355</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>302</v>
+        <v>356</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>303</v>
+        <v>357</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>267</v>
+        <v>318</v>
       </c>
       <c r="B2" s="3">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>304</v>
+        <v>358</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>263</v>
+        <v>323</v>
       </c>
       <c r="B3" s="3">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>305</v>
+        <v>359</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>306</v>
+        <v>334</v>
       </c>
       <c r="B4" s="3">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>307</v>
+        <v>360</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>278</v>
+        <v>361</v>
       </c>
       <c r="B5" s="3">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>308</v>
+        <v>362</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>309</v>
+        <v>272</v>
       </c>
       <c r="B6" s="3">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>310</v>
+        <v>363</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>311</v>
+        <v>364</v>
       </c>
       <c r="B7" s="3">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>312</v>
+        <v>365</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>199</v>
+        <v>329</v>
       </c>
       <c r="B8" s="3">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>313</v>
+        <v>366</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>273</v>
+        <v>367</v>
       </c>
       <c r="B9" s="3">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>314</v>
+        <v>368</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>158</v>
+        <v>236</v>
       </c>
       <c r="B10" s="3">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>315</v>
+        <v>369</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>316</v>
+        <v>370</v>
       </c>
       <c r="B11" s="3">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>317</v>
+        <v>371</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>285</v>
+        <v>372</v>
       </c>
       <c r="B12" s="3">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>318</v>
+        <v>373</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>319</v>
+        <v>374</v>
       </c>
       <c r="B13" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>320</v>
+        <v>375</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>321</v>
+        <v>230</v>
       </c>
       <c r="B14" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>322</v>
+        <v>376</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>323</v>
+        <v>377</v>
       </c>
       <c r="B15" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>318</v>
+        <v>378</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>324</v>
+        <v>379</v>
       </c>
       <c r="B16" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>325</v>
+        <v>380</v>
       </c>
     </row>
   </sheetData>
@@ -4699,10 +5648,10 @@
         <v>37</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>326</v>
+        <v>381</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>327</v>
+        <v>382</v>
       </c>
     </row>
     <row r="2">
@@ -4710,10 +5659,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>328</v>
+        <v>383</v>
       </c>
     </row>
     <row r="3">
@@ -4721,10 +5670,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>329</v>
+        <v>384</v>
       </c>
     </row>
     <row r="4">
@@ -4735,7 +5684,7 @@
         <v>6</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>330</v>
+        <v>385</v>
       </c>
     </row>
     <row r="5">
@@ -4746,7 +5695,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>331</v>
+        <v>386</v>
       </c>
     </row>
   </sheetData>
@@ -4767,13 +5716,13 @@
         <v>40</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>332</v>
+        <v>387</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>333</v>
+        <v>388</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>334</v>
+        <v>389</v>
       </c>
     </row>
     <row r="2">
@@ -4784,7 +5733,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>335</v>
+        <v>390</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -4793,10 +5742,10 @@
         <v>30</v>
       </c>
       <c r="B3" s="3">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>335</v>
+        <v>390</v>
       </c>
       <c r="D3" s="3"/>
     </row>
@@ -4805,10 +5754,10 @@
         <v>32</v>
       </c>
       <c r="B4" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>335</v>
+        <v>390</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W27.xlsx
+++ b/reports/devops-juniors-israel-2026-W27.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="376">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-06-30T09:58:17</t>
+    <t xml:space="preserve">2026-07-01T10:08:50</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -103,6 +103,9 @@
     <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
   </si>
   <si>
+    <t xml:space="preserve">Junior DevOps</t>
+  </si>
+  <si>
     <t xml:space="preserve">By source</t>
   </si>
   <si>
@@ -163,6 +166,24 @@
     <t xml:space="preserve">2026-06-02</t>
   </si>
   <si>
+    <t xml:space="preserve">Junior IT DevOps Engineer - Temporary Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-devops-engineer-temporary-position-at-mobileye-4417802849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-25</t>
+  </si>
+  <si>
     <t xml:space="preserve">Linux System Administrator</t>
   </si>
   <si>
@@ -214,520 +235,790 @@
     <t xml:space="preserve">2026-06-12</t>
   </si>
   <si>
-    <t xml:space="preserve">SW DevOps and Test Infrastructure Student, Nitro SW Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amazon Web Services (AWS)</t>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Kubernetes, Terraform/IaC, Networking, Virtualization, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-sela-4428931319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Inclined Systems Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SB0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-inclined-systems-engineer-at-sb0-4429860196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-4433428247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-ai-4430612805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peak Innovation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, Cloud (any), Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-peak-innovation-4431041046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator – Advanced Data Center and AI Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-ai-4427315937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator &amp; IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inManage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eToro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-etoro-4434952696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmit Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-transmit-security-4409875183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Corp System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payoneer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.payoneer.com/careers/position/7916835/?gh_jid=7916835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-at-paragon-4417886377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Operations &amp; Helpdesk Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claroty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-helpdesk-engineer-at-claroty-4412805136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashdod, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Kubernetes, Networking, Virtualization, Active Directory, Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-sqlink-group-4431944036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk and System Administrator (Israel)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Terraform/IaC, Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-and-system-administrator-israel-at-zota-4431223683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MyHeritage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-myheritage-4434704007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Help Desk (student position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LiveU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-student-position-at-liveu-4434277505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Innoviz Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-innoviz-technologies-4407119527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spinomenal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-spinomenal-4431228721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check Point Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Cloud (any), Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-administrator-at-check-point-software-4427626178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Korentec Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-yael-korentec-technologies-4431373486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4430443104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Desktop Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zensar Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-at-zensar-technologies-4418821535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silverfort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-desk-specialist-at-silverfort-4434301874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Service Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMAREL LTD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-amarel-ltd-4428035454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riverside</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-riverside-4409620033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk &amp; IT Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mize</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-it-administrator-at-mize-4425999700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4431915164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk (24892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-24892-at-yael-group-4427354216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nova Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-nova-ltd-4413884631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Bootcamp Course</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-at-abra-4432200564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student for Strength and Dynamics Analysis team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-for-strength-and-dynamics-analysis-team-at-elbit-systems-israel-4421930557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tata Consultancy Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-tata-consultancy-services-4430592021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk (Temporary)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personetics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-temporary-at-personetics-4428653392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vectorious Medical Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-vectorious-medical-technologies-4434451066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">איש/אשת Help Desk Tier 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Webox LTD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%90%D7%99%D7%A9-%D7%90%D7%A9%D7%AA-help-desk-tier-1-at-webox-ltd-4430232360</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RealPlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helpdesk Specialist &amp; System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">365Scores</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/helpdesk-specialist-system-administrator-at-365scores-4431701042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Support Representative</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weizmann Institute of Science</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-representative-at-weizmann-institute-of-science-4431080100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Infrastructure &amp; Support Specialist (Tier 2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moveo Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-support-specialist-tier-2-at-moveo-source-4434338174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4425017778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wobi Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-junior-at-wobi-ltd-4419670684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician (Part-Time)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential Careers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-part-time-at-confidential-careers-4425768937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-sqlink-group-4429856103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Log-On Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-log-on-software-4432333769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zoho</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-zoho-4427961067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AudioCodes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4395665709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WSC Sports</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-wsc-sports-4415703367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-abra-4423876931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist (Part time )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvei</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-part-time-at-nuvei-4421067573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aeronautical Information Service Cadet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grenada Airports Authority</t>
+  </si>
+  <si>
+    <t xml:space="preserve">St. George's,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-aeronautical-information-service-cadet-grenada-airports-authority-1134169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">תומך/ת Help Desk וטכנאי/ת PC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accel Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%AA%D7%95%D7%9E%D7%9A-%D7%AA-help-desk%C2%A0%D7%95%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-pc-at-accel-solutions-4431094783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">טכנאי/ת Help desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4410001855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service Desk Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-desk-operator-at-tata-consultancy-services-4427424594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M.D. Mechanical Devices Ltd.</t>
   </si>
   <si>
     <t xml:space="preserve">Haifa, Haifa District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Terraform/IaC, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sw-devops-and-test-infrastructure-student-nitro-sw-team-at-amazon-web-services-aws-4432816876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC &amp; SOC Analyst</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Commit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-soc-analyst-at-commit-4421804878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-ai-4430612805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-4433428247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peak Innovation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, Cloud (any), Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-peak-innovation-4431041046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experienced IT System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iFOR FINTECH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/experienced-it-system-administrator-at-ifor-fintech-4428923734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator – Advanced Data Center and AI Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-ai-4427315937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator &amp; IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inManage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Corp System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Payoneer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.payoneer.com/careers/position/7916835/?gh_jid=7916835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Infrastructure &amp; Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Squadron Israel - Hatayeset</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Cloud (any), Git, Terraform/IaC, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infrastructure-technical-support-specialist-at-the-squadron-israel-hatayeset-4421938671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Operations Student - Nights &amp; Weekend shifts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Voyantis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Git, Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-operations-student-nights-weekend-shifts-at-voyantis-4422723294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shavit Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Kubernetes, Networking, Monitoring, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-shavit-software-4426784526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-at-paragon-4417886377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Engineer - Intern position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Align Technology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Cloud (any), Monitoring, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-intern-position-at-align-technology-4303646784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashdod, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Kubernetes, Networking, Virtualization, Active Directory, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-sqlink-group-4432227642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk and System Administrator (Israel)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Terraform/IaC, Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-and-system-administrator-israel-at-zota-4431223683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MyHeritage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-myheritage-4434704007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Droxi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-operations-engineer-at-droxi-4426788584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Menora Mivtachim Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-menora-mivtachim-group-4434972024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Help Desk (student position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LiveU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-student-position-at-liveu-4434277505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spinomenal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-spinomenal-4431228721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Innoviz Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-innoviz-technologies-4407119527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Korentec Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-yael-korentec-technologies-4431373486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4430443104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Desktop Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zensar Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-at-zensar-technologies-4418821535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator - JB-651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PwC Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system%C2%A0administrator-jb-651-at-pwc-israel-4429917341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Service Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer (35684)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-35684-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4434276396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMAREL LTD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-amarel-ltd-4428035454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk (24892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-24892-at-yael-group-4427354216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Network Operations Center Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tata Consultancy Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-operations-center-operator-at-tata-consultancy-services-4413535925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Bootcamp Course</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Git</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-at-abra-4432200564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4406043821</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-m-d-mechanical-devices-ltd-4420118096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oktopost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-oktopost-4431366669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Customer Support Helpdesk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Empathy Talent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">California, California, United States</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-customer-support-helpdesk-specialist-empathy-talent-1134244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Customer Support Technician Helpdesk Offboardings &amp;amp; Access</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pixel Machinery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-customer-support-technician-helpdesk-offboardings-amp-access-pixel-machinery-1134154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineering-student-at-elbit-systems-israel-4414854587</t>
   </si>
   <si>
     <t xml:space="preserve">IT Support Administrator</t>
@@ -736,375 +1027,39 @@
     <t xml:space="preserve">Plarium</t>
   </si>
   <si>
-    <t xml:space="preserve">Azure, Networking</t>
+    <t xml:space="preserve">yes</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-administrator-at-plarium-4431096159</t>
   </si>
   <si>
-    <t xml:space="preserve">טכנאי/ת Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4427161897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-tata-consultancy-services-4430592021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Specialist - JB-594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-jb-594-at-pwc-israel-4429922813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk (Temporary)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Personetics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-temporary-at-personetics-4428653392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">איש/אשת Help Desk Tier 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Webox LTD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%90%D7%99%D7%A9-%D7%90%D7%A9%D7%AA-help-desk-tier-1-at-webox-ltd-4430232360</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ONE Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-one-technologies-4432205195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Support Representative</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weizmann Institute of Science</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-representative-at-weizmann-institute-of-science-4431080100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Engineer- Student Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global-e</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-student-position-at-global-e-4378147513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft System Administrator (36014)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-administrator-36014-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4434285138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4425017778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wobi Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-junior-at-wobi-ltd-4419670684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician (Part-Time)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential Careers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-part-time-at-confidential-careers-4425768937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-sqlink-group-4429856103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AudioCodes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4395665709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WSC Sports</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-wsc-sports-4415703367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-abra-4423876931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zoho</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-zoho-4427961067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Multimedia Systems &amp; IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deloitte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/multimedia-systems-it-support-specialist-at-deloitte-4433302126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist (Part time )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvei</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-part-time-at-nuvei-4421067573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Operations Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unity3D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://unity.com/careers/positions/7860478?gh_jid=7860478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Analyst (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential</t>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roles requiring it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What to learn / where to start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
   </si>
   <si>
     <t xml:space="preserve">Networking</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-analyst-student-position-at-confidential-4429852518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aeronautical Information Service Cadet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grenada Airports Authority</t>
-  </si>
-  <si>
-    <t xml:space="preserve">St. George's,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-aeronautical-information-service-cadet-grenada-airports-authority-1134169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developer Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://unity.com/careers/positions/7543658?gh_jid=7543658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist (28516)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-28516-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4434281333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Service Desk Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-desk-operator-at-tata-consultancy-services-4427424594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">תומך/ת Help Desk וטכנאי/ת PC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Accel Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%AA%D7%95%D7%9E%D7%9A-%D7%AA-help-desk%C2%A0%D7%95%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-pc-at-accel-solutions-4431094783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oktopost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-oktopost-4431366669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Customer Support Helpdesk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Empathy Talent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">California, California, United States</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-customer-support-helpdesk-specialist-empathy-talent-1134244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Customer Support Technician Helpdesk Offboardings &amp;amp; Access</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pixel Machinery</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-customer-support-technician-helpdesk-offboardings-amp-access-pixel-machinery-1134154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scheduling Coordinator Entry Level No Experience Needed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Travel Planning Professionals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New York, New York, United States</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-scheduling-coordinator-entry-level-no-experience-needed-travel-planning-professionals-1134108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roles requiring it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What to learn / where to start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
   </si>
   <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
+  </si>
+  <si>
     <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
   </si>
   <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
-  </si>
-  <si>
     <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
   </si>
   <si>
@@ -1114,28 +1069,37 @@
     <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
   </si>
   <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
+  </si>
+  <si>
     <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
   </si>
   <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Virtualization</t>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
   </si>
   <si>
     <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
   </si>
   <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
   </si>
   <si>
     <t xml:space="preserve">AWS</t>
@@ -1144,19 +1108,10 @@
     <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pro Git book (free online) + create a learning repo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
   </si>
   <si>
     <t xml:space="preserve">Count</t>
@@ -1177,6 +1132,9 @@
     <t xml:space="preserve">Often paired with on-call. Strong learning track.</t>
   </si>
   <si>
+    <t xml:space="preserve">Direct DevOps role — apply aggressively. Rare and competitive.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jobs</t>
   </si>
   <si>
@@ -1184,9 +1142,6 @@
   </si>
   <si>
     <t xml:space="preserve">Error</t>
-  </si>
-  <si>
-    <t xml:space="preserve">yes</t>
   </si>
 </sst>
 </file>
@@ -1311,7 +1266,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7">
@@ -1319,7 +1274,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -1327,7 +1282,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>33</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9">
@@ -1335,7 +1290,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>361</v>
+        <v>369</v>
       </c>
     </row>
     <row r="10">
@@ -1417,7 +1372,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>38</v>
+        <v>45</v>
       </c>
     </row>
     <row r="22">
@@ -1425,7 +1380,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>27</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23">
@@ -1433,7 +1388,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
@@ -1445,29 +1400,29 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3"/>
-      <c r="B25" s="3"/>
+      <c r="A25" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B25" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="s">
-        <v>29</v>
-      </c>
+      <c r="A26" s="3"/>
       <c r="B26" s="3"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B27" s="3">
-        <v>63</v>
-      </c>
+      <c r="B27" s="3"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
         <v>31</v>
       </c>
       <c r="B28" s="3">
-        <v>6</v>
+        <v>62</v>
       </c>
     </row>
     <row r="29">
@@ -1476,6 +1431,14 @@
       </c>
       <c r="B29" s="3">
         <v>4</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B30" s="3">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -1487,8 +1450,8 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="33" customWidth="1"/>
-    <col min="4" max="4" width="43" customWidth="1"/>
+    <col min="3" max="3" width="31" customWidth="1"/>
+    <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
     <col min="7" max="7" width="60" customWidth="1"/>
@@ -1499,34 +1462,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2">
@@ -1534,13 +1497,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>28</v>
@@ -1549,16 +1512,16 @@
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3">
@@ -1566,31 +1529,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4">
@@ -1598,13 +1561,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>26</v>
@@ -1613,16 +1576,16 @@
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5">
@@ -1630,13 +1593,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>26</v>
@@ -1645,16 +1608,16 @@
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6">
@@ -1662,31 +1625,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F6" s="3">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7">
@@ -1694,31 +1657,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F7" s="3">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>59</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8">
@@ -1726,13 +1689,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>26</v>
@@ -1741,16 +1704,16 @@
         <v>76</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9">
@@ -1758,13 +1721,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>26</v>
@@ -1773,16 +1736,16 @@
         <v>76</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10">
@@ -1790,31 +1753,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10" s="3">
+        <v>76</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F10" s="3">
-        <v>57</v>
-      </c>
-      <c r="G10" s="3" t="s">
+      <c r="H10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="J10" s="3" t="s">
         <v>87</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="11">
@@ -1822,31 +1785,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F11" s="3">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>59</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12">
@@ -1854,31 +1817,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F12" s="3">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13">
@@ -1886,13 +1849,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>26</v>
@@ -1901,16 +1864,16 @@
         <v>52</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14">
@@ -1918,13 +1881,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>26</v>
@@ -1933,16 +1896,16 @@
         <v>52</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15">
@@ -1950,31 +1913,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F15" s="3">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -1982,31 +1945,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>45</v>
+        <v>114</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F16" s="3">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>115</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17">
@@ -2014,31 +1977,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>117</v>
       </c>
       <c r="D17" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F17" s="3">
+        <v>47</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="E17" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F17" s="3">
-        <v>44</v>
-      </c>
-      <c r="G17" s="3" t="s">
+      <c r="J17" s="3" t="s">
         <v>119</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="18">
@@ -2046,31 +2009,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F18" s="3">
         <v>44</v>
       </c>
       <c r="G18" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="J18" s="3" t="s">
         <v>124</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="19">
@@ -2078,31 +2041,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>127</v>
+        <v>68</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>128</v>
+        <v>69</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F19" s="3">
         <v>44</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20">
@@ -2110,13 +2073,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>61</v>
+        <v>129</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>25</v>
@@ -2125,16 +2088,16 @@
         <v>44</v>
       </c>
       <c r="G20" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="J20" s="3" t="s">
         <v>132</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="21">
@@ -2142,13 +2105,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="D21" s="3" t="s">
         <v>134</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>73</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>26</v>
@@ -2157,16 +2120,16 @@
         <v>40</v>
       </c>
       <c r="G21" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>137</v>
-      </c>
       <c r="J21" s="3" t="s">
-        <v>138</v>
+        <v>112</v>
       </c>
     </row>
     <row r="22">
@@ -2174,31 +2137,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>60</v>
+        <v>137</v>
       </c>
       <c r="C22" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F22" s="3">
+        <v>34</v>
+      </c>
+      <c r="G22" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="H22" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F22" s="3">
-        <v>40</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>142</v>
-      </c>
       <c r="J22" s="3" t="s">
-        <v>143</v>
+        <v>77</v>
       </c>
     </row>
     <row r="23">
@@ -2206,13 +2169,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>62</v>
+        <v>143</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>25</v>
@@ -2221,16 +2184,16 @@
         <v>34</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>143</v>
+        <v>66</v>
       </c>
     </row>
     <row r="24">
@@ -2238,31 +2201,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="E24" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F24" s="3">
+        <v>30</v>
+      </c>
+      <c r="G24" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="H24" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F24" s="3">
-        <v>34</v>
-      </c>
-      <c r="G24" s="3" t="s">
+      <c r="J24" s="3" t="s">
         <v>151</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="25">
@@ -2270,31 +2233,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="D25" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="E25" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F25" s="3">
+        <v>30</v>
+      </c>
+      <c r="G25" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="E25" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F25" s="3">
-        <v>32</v>
-      </c>
-      <c r="G25" s="3" t="s">
+      <c r="H25" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I25" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="H25" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I25" s="3" t="s">
+      <c r="J25" s="3" t="s">
         <v>157</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="26">
@@ -2302,31 +2265,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>158</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F26" s="3">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>159</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>160</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>59</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -2365,7 +2328,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="2" max="2" width="33" customWidth="1"/>
     <col min="3" max="3" width="44" customWidth="1"/>
     <col min="4" max="4" width="31" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
@@ -2382,16 +2345,16 @@
         <v>161</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>162</v>
@@ -2400,13 +2363,13 @@
         <v>163</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>164</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>165</v>
@@ -2414,13 +2377,13 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>28</v>
@@ -2429,54 +2392,54 @@
         <v>100</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>166</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K2" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E3" s="3">
         <v>100</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>166</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K3" s="3">
         <v>37</v>
@@ -2484,13 +2447,13 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>26</v>
@@ -2499,33 +2462,33 @@
         <v>100</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>166</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K4" s="3">
-        <v>0</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>26</v>
@@ -2534,103 +2497,103 @@
         <v>100</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>166</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K5" s="3">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E6" s="3">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>166</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="K6" s="3">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E7" s="3">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>166</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="K7" s="3">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>26</v>
@@ -2639,33 +2602,33 @@
         <v>76</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>166</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="K8" s="3">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>26</v>
@@ -2674,138 +2637,138 @@
         <v>76</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>166</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="K9" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" s="3">
+        <v>76</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E10" s="3">
-        <v>57</v>
-      </c>
-      <c r="F10" s="3" t="s">
+      <c r="G10" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="J10" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>89</v>
-      </c>
       <c r="K10" s="3">
-        <v>46</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E11" s="3">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>166</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>59</v>
+        <v>95</v>
       </c>
       <c r="K11" s="3">
-        <v>0</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E12" s="3">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>166</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="K12" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>26</v>
@@ -2814,33 +2777,33 @@
         <v>52</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>166</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K13" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>26</v>
@@ -2849,42 +2812,42 @@
         <v>52</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>166</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="K14" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E15" s="3">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>166</v>
@@ -2893,164 +2856,164 @@
         <v>31</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="K15" s="3">
-        <v>46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>45</v>
+        <v>114</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E16" s="3">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>166</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="K16" s="3">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>117</v>
       </c>
       <c r="C17" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" s="3">
+        <v>47</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E17" s="3">
-        <v>44</v>
-      </c>
-      <c r="F17" s="3" t="s">
+      <c r="J17" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H17" s="3" t="s">
+      <c r="K17" s="3">
         <v>30</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="K17" s="3">
-        <v>19</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E18" s="3">
         <v>44</v>
       </c>
       <c r="F18" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="J18" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>59</v>
-      </c>
       <c r="K18" s="3">
-        <v>0</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>127</v>
+        <v>68</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>128</v>
+        <v>69</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E19" s="3">
         <v>44</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>166</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="K19" s="3">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>61</v>
+        <v>129</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>25</v>
@@ -3059,33 +3022,33 @@
         <v>44</v>
       </c>
       <c r="F20" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="J20" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>48</v>
-      </c>
       <c r="K20" s="3">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>134</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>73</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>26</v>
@@ -3094,68 +3057,68 @@
         <v>40</v>
       </c>
       <c r="F21" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>137</v>
-      </c>
       <c r="J21" s="3" t="s">
-        <v>138</v>
+        <v>112</v>
       </c>
       <c r="K21" s="3">
-        <v>41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>60</v>
+        <v>137</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E22" s="3">
+        <v>34</v>
+      </c>
+      <c r="F22" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="G22" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E22" s="3">
-        <v>40</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>142</v>
-      </c>
       <c r="J22" s="3" t="s">
-        <v>143</v>
+        <v>77</v>
       </c>
       <c r="K22" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>62</v>
+        <v>143</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>25</v>
@@ -3164,109 +3127,109 @@
         <v>34</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>166</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>143</v>
+        <v>66</v>
       </c>
       <c r="K23" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="D24" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E24" s="3">
+        <v>30</v>
+      </c>
+      <c r="F24" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="G24" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E24" s="3">
-        <v>34</v>
-      </c>
-      <c r="F24" s="3" t="s">
+      <c r="J24" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>59</v>
-      </c>
       <c r="K24" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="B25" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="C25" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="D25" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E25" s="3">
+        <v>30</v>
+      </c>
+      <c r="F25" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="D25" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E25" s="3">
-        <v>32</v>
-      </c>
-      <c r="F25" s="3" t="s">
+      <c r="G25" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I25" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="G25" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I25" s="3" t="s">
+      <c r="J25" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="J25" s="3" t="s">
-        <v>121</v>
-      </c>
       <c r="K25" s="3">
-        <v>19</v>
+        <v>31</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>158</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E26" s="3">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>159</v>
@@ -3275,16 +3238,16 @@
         <v>166</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>160</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="K26" s="3">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27">
@@ -3295,7 +3258,7 @@
         <v>168</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>169</v>
+        <v>69</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>25</v>
@@ -3304,313 +3267,313 @@
         <v>30</v>
       </c>
       <c r="F27" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I27" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>171</v>
-      </c>
       <c r="J27" s="3" t="s">
-        <v>172</v>
+        <v>72</v>
       </c>
       <c r="K27" s="3">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E28" s="3">
+        <v>28</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I28" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="J28" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="C28" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E28" s="3">
-        <v>30</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="J28" s="3" t="s">
-        <v>143</v>
-      </c>
       <c r="K28" s="3">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B29" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E29" s="3">
+        <v>27</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I29" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="J29" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E29" s="3">
-        <v>30</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>182</v>
-      </c>
       <c r="K29" s="3">
-        <v>30</v>
+        <v>13</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E30" s="3">
+        <v>27</v>
+      </c>
+      <c r="F30" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="G30" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I30" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="C30" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E30" s="3">
-        <v>28</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>186</v>
-      </c>
       <c r="J30" s="3" t="s">
-        <v>138</v>
+        <v>157</v>
       </c>
       <c r="K30" s="3">
-        <v>41</v>
+        <v>31</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>49</v>
+        <v>185</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E31" s="3">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F31" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I31" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="G31" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I31" s="3" t="s">
-        <v>189</v>
-      </c>
       <c r="J31" s="3" t="s">
-        <v>190</v>
+        <v>95</v>
       </c>
       <c r="K31" s="3">
-        <v>8</v>
+        <v>47</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E32" s="3">
+        <v>23</v>
+      </c>
+      <c r="F32" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="G32" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I32" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="C32" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E32" s="3">
-        <v>27</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>194</v>
-      </c>
       <c r="J32" s="3" t="s">
-        <v>195</v>
+        <v>112</v>
       </c>
       <c r="K32" s="3">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E33" s="3">
+        <v>20</v>
+      </c>
+      <c r="F33" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="G33" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I33" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="C33" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E33" s="3">
-        <v>27</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>200</v>
-      </c>
       <c r="J33" s="3" t="s">
-        <v>182</v>
+        <v>95</v>
       </c>
       <c r="K33" s="3">
-        <v>30</v>
+        <v>47</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>126</v>
+        <v>82</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E34" s="3">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>166</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="K34" s="3">
-        <v>46</v>
+        <v>14</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>204</v>
+        <v>107</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>128</v>
+        <v>69</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E35" s="3">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>166</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>195</v>
+        <v>95</v>
       </c>
       <c r="K35" s="3">
-        <v>12</v>
+        <v>47</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>210</v>
+        <v>69</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>25</v>
@@ -3619,7 +3582,7 @@
         <v>20</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>166</v>
@@ -3628,80 +3591,80 @@
         <v>31</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>89</v>
+        <v>208</v>
       </c>
       <c r="K36" s="3">
-        <v>46</v>
+        <v>21</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E37" s="3">
+        <v>17</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I37" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E37" s="3">
-        <v>20</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="G37" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I37" s="3" t="s">
-        <v>216</v>
-      </c>
       <c r="J37" s="3" t="s">
-        <v>81</v>
+        <v>112</v>
       </c>
       <c r="K37" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>76</v>
+        <v>214</v>
       </c>
       <c r="B38" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E38" s="3">
+        <v>17</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I38" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="C38" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E38" s="3">
-        <v>20</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I38" s="3" t="s">
-        <v>218</v>
-      </c>
       <c r="J38" s="3" t="s">
-        <v>101</v>
+        <v>179</v>
       </c>
       <c r="K38" s="3">
         <v>13</v>
@@ -3709,83 +3672,83 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="C39" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="D39" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E39" s="3">
+        <v>16</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I39" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="C39" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E39" s="3">
-        <v>17</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H39" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I39" s="3" t="s">
-        <v>222</v>
-      </c>
       <c r="J39" s="3" t="s">
-        <v>195</v>
+        <v>95</v>
       </c>
       <c r="K39" s="3">
-        <v>12</v>
+        <v>47</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E40" s="3">
+        <v>13</v>
+      </c>
+      <c r="F40" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="G40" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I40" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="J40" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="D40" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E40" s="3">
-        <v>16</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I40" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="J40" s="3" t="s">
-        <v>59</v>
-      </c>
       <c r="K40" s="3">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>229</v>
+        <v>211</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>27</v>
@@ -3794,138 +3757,138 @@
         <v>13</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>166</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="K41" s="3">
-        <v>7</v>
+        <v>23</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E42" s="3">
+        <v>10</v>
+      </c>
+      <c r="F42" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="G42" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I42" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="C42" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E42" s="3">
-        <v>13</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>237</v>
-      </c>
       <c r="J42" s="3" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="K42" s="3">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>238</v>
+        <v>141</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E43" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>166</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>59</v>
+        <v>225</v>
       </c>
       <c r="K43" s="3">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E44" s="3">
+        <v>10</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I44" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="J44" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="C44" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E44" s="3">
-        <v>13</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>121</v>
-      </c>
       <c r="K44" s="3">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="C45" s="3" t="s">
         <v>246</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>248</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>25</v>
@@ -3934,7 +3897,7 @@
         <v>10</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>166</v>
@@ -3943,24 +3906,24 @@
         <v>31</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>53</v>
+        <v>112</v>
       </c>
       <c r="K45" s="3">
-        <v>37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>148</v>
+        <v>248</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>224</v>
+        <v>249</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>62</v>
+        <v>109</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>25</v>
@@ -3969,33 +3932,33 @@
         <v>10</v>
       </c>
       <c r="F46" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I46" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="G46" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I46" s="3" t="s">
+      <c r="J46" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>232</v>
-      </c>
       <c r="K46" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B47" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="B47" s="3" t="s">
-        <v>205</v>
-      </c>
       <c r="C47" s="3" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>25</v>
@@ -4004,33 +3967,33 @@
         <v>10</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>166</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>195</v>
+        <v>60</v>
       </c>
       <c r="K47" s="3">
-        <v>12</v>
+        <v>38</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>257</v>
+        <v>69</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>25</v>
@@ -4039,33 +4002,33 @@
         <v>10</v>
       </c>
       <c r="F48" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I48" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="G48" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>259</v>
-      </c>
       <c r="J48" s="3" t="s">
-        <v>260</v>
+        <v>112</v>
       </c>
       <c r="K48" s="3">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>175</v>
+        <v>219</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>25</v>
@@ -4074,33 +4037,33 @@
         <v>10</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>166</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>265</v>
+        <v>151</v>
       </c>
       <c r="K49" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>73</v>
+        <v>265</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>25</v>
@@ -4109,138 +4072,138 @@
         <v>10</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>263</v>
+        <v>233</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>166</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>232</v>
+        <v>112</v>
       </c>
       <c r="K50" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E51" s="3">
+        <v>6</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I51" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="B51" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E51" s="3">
-        <v>10</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="G51" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H51" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I51" s="3" t="s">
-        <v>273</v>
-      </c>
       <c r="J51" s="3" t="s">
-        <v>172</v>
+        <v>229</v>
       </c>
       <c r="K51" s="3">
-        <v>1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E52" s="3">
+        <v>6</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="J52" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="B52" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E52" s="3">
-        <v>8</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>59</v>
-      </c>
       <c r="K52" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>214</v>
+        <v>276</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E53" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>166</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>81</v>
+        <v>243</v>
       </c>
       <c r="K53" s="3">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>281</v>
+        <v>141</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>201</v>
+        <v>133</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>91</v>
+        <v>143</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>25</v>
@@ -4249,33 +4212,33 @@
         <v>6</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="G54" s="3" t="s">
         <v>166</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>284</v>
+        <v>77</v>
       </c>
       <c r="K54" s="3">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>285</v>
+        <v>141</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>175</v>
+        <v>74</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>25</v>
@@ -4284,33 +4247,33 @@
         <v>6</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>287</v>
+        <v>268</v>
       </c>
       <c r="G55" s="3" t="s">
         <v>166</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>289</v>
+        <v>112</v>
       </c>
       <c r="K55" s="3">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>91</v>
+        <v>246</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>25</v>
@@ -4319,33 +4282,33 @@
         <v>6</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="G56" s="3" t="s">
         <v>166</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>260</v>
+        <v>132</v>
       </c>
       <c r="K56" s="3">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>148</v>
+        <v>286</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>139</v>
+        <v>287</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>25</v>
@@ -4354,33 +4317,33 @@
         <v>6</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>293</v>
+        <v>268</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>166</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>143</v>
+        <v>60</v>
       </c>
       <c r="K57" s="3">
-        <v>6</v>
+        <v>38</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>266</v>
+        <v>244</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>150</v>
+        <v>290</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>25</v>
@@ -4389,33 +4352,33 @@
         <v>6</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>166</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>53</v>
+        <v>157</v>
       </c>
       <c r="K58" s="3">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>298</v>
+        <v>186</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>155</v>
+        <v>74</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>25</v>
@@ -4430,27 +4393,27 @@
         <v>166</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>182</v>
+        <v>295</v>
       </c>
       <c r="K59" s="3">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>201</v>
+        <v>297</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>25</v>
@@ -4459,118 +4422,118 @@
         <v>6</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>166</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="K60" s="3">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E61" s="3">
+        <v>4</v>
+      </c>
+      <c r="F61" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="B61" s="3" t="s">
+      <c r="G61" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I61" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="C61" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E61" s="3">
-        <v>6</v>
-      </c>
-      <c r="F61" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="G61" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H61" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I61" s="3" t="s">
-        <v>306</v>
-      </c>
       <c r="J61" s="3" t="s">
-        <v>307</v>
+        <v>87</v>
       </c>
       <c r="K61" s="3">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E62" s="3">
+        <v>3</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I62" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="B62" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="D62" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E62" s="3">
-        <v>6</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>310</v>
-      </c>
       <c r="J62" s="3" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="K62" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="C63" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="B63" s="3" t="s">
+      <c r="D63" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E63" s="3">
+        <v>3</v>
+      </c>
+      <c r="F63" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="C63" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E63" s="3">
-        <v>6</v>
-      </c>
-      <c r="F63" s="3" t="s">
-        <v>282</v>
-      </c>
       <c r="G63" s="3" t="s">
         <v>166</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I63" s="3" t="s">
         <v>313</v>
@@ -4579,7 +4542,7 @@
         <v>314</v>
       </c>
       <c r="K63" s="3">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="64">
@@ -4587,115 +4550,115 @@
         <v>315</v>
       </c>
       <c r="B64" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="C64" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="C64" s="3" t="s">
+      <c r="D64" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E64" s="3">
+        <v>3</v>
+      </c>
+      <c r="F64" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="D64" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E64" s="3">
-        <v>4</v>
-      </c>
-      <c r="F64" s="3" t="s">
+      <c r="G64" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I64" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="G64" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H64" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I64" s="3" t="s">
+      <c r="J64" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="J64" s="3" t="s">
-        <v>320</v>
-      </c>
       <c r="K64" s="3">
-        <v>33</v>
+        <v>15</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="C65" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="B65" s="3" t="s">
+      <c r="D65" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E65" s="3">
+        <v>3</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I65" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="C65" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="D65" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E65" s="3">
-        <v>4</v>
-      </c>
-      <c r="F65" s="3" t="s">
+      <c r="J65" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="G65" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H65" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I65" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="J65" s="3" t="s">
-        <v>325</v>
-      </c>
       <c r="K65" s="3">
-        <v>5</v>
+        <v>27</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>326</v>
+        <v>152</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>328</v>
+        <v>290</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E66" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>329</v>
+        <v>317</v>
       </c>
       <c r="G66" s="3" t="s">
         <v>166</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="K66" s="3">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>25</v>
@@ -4704,33 +4667,33 @@
         <v>3</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G67" s="3" t="s">
         <v>166</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="K67" s="3">
-        <v>37</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>214</v>
+        <v>331</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>91</v>
+        <v>328</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>25</v>
@@ -4739,234 +4702,92 @@
         <v>3</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>334</v>
+        <v>317</v>
       </c>
       <c r="G68" s="3" t="s">
         <v>166</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="K68" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E69" s="3">
-        <v>3</v>
-      </c>
-      <c r="F69" s="3" t="s">
-        <v>318</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
         <v>166</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>338</v>
+        <v>55</v>
       </c>
       <c r="K69" s="3">
-        <v>14</v>
+        <v>37</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>229</v>
+        <v>46</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E70" s="3">
-        <v>3</v>
-      </c>
-      <c r="F70" s="3" t="s">
-        <v>334</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
-        <v>166</v>
+        <v>337</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="K70" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="D71" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E71" s="3">
-        <v>3</v>
-      </c>
-      <c r="F71" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="G71" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H71" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I71" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="J71" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="K71" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="D72" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E72" s="3">
-        <v>3</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="K72" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="D73" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E73" s="3">
-        <v>3</v>
-      </c>
-      <c r="F73" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="G73" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H73" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I73" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="J73" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="K73" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="D74" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E74" s="3">
-        <v>0</v>
-      </c>
-      <c r="F74" s="3"/>
-      <c r="G74" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H74" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I74" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="J74" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="K74" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K74"/>
+  <autoFilter ref="A1:K70"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -5037,10 +4858,6 @@
     <hyperlink ref="I68" r:id="rId67"/>
     <hyperlink ref="I69" r:id="rId68"/>
     <hyperlink ref="I70" r:id="rId69"/>
-    <hyperlink ref="I71" r:id="rId70"/>
-    <hyperlink ref="I72" r:id="rId71"/>
-    <hyperlink ref="I73" r:id="rId72"/>
-    <hyperlink ref="I74" r:id="rId73"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5048,8 +4865,8 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="58" customWidth="1"/>
-    <col min="2" max="2" width="27" customWidth="1"/>
+    <col min="1" max="1" width="49" customWidth="1"/>
+    <col min="2" max="2" width="33" customWidth="1"/>
     <col min="3" max="3" width="25" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
@@ -5059,16 +4876,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>162</v>
@@ -5077,356 +4894,195 @@
         <v>164</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>54</v>
+        <v>107</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>55</v>
+        <v>108</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D2" s="3">
-        <v>100</v>
+        <v>51</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>57</v>
+        <v>110</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>58</v>
+        <v>111</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>59</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>67</v>
+        <v>133</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D3" s="3">
-        <v>92</v>
+        <v>40</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>69</v>
+        <v>135</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>70</v>
+        <v>136</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>59</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>71</v>
+        <v>189</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>72</v>
+        <v>190</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D4" s="3">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>74</v>
+        <v>191</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>75</v>
+        <v>192</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>59</v>
+        <v>112</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>76</v>
+        <v>209</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>90</v>
+        <v>210</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D5" s="3">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>92</v>
+        <v>212</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>93</v>
+        <v>213</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>59</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>94</v>
+        <v>244</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>95</v>
+        <v>245</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D6" s="3">
-        <v>52</v>
+        <v>10</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>96</v>
+        <v>236</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>97</v>
+        <v>247</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>59</v>
+        <v>112</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>102</v>
+        <v>256</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>103</v>
+        <v>257</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D7" s="3">
-        <v>52</v>
+        <v>10</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>104</v>
+        <v>236</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>105</v>
+        <v>258</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>59</v>
+        <v>112</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>122</v>
+        <v>263</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>123</v>
+        <v>264</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D8" s="3">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>124</v>
+        <v>233</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>125</v>
+        <v>266</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>59</v>
+        <v>112</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>127</v>
+        <v>280</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D9" s="3">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>129</v>
+        <v>268</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>130</v>
+        <v>281</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D10" s="3">
-        <v>34</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D11" s="3">
-        <v>32</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D12" s="3">
-        <v>16</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D13" s="3">
-        <v>13</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D14" s="3">
-        <v>8</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D15" s="3">
-        <v>3</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D16" s="3">
-        <v>3</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>59</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G16"/>
+  <autoFilter ref="A1:G9"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
@@ -5436,13 +5092,6 @@
     <hyperlink ref="F7" r:id="rId6"/>
     <hyperlink ref="F8" r:id="rId7"/>
     <hyperlink ref="F9" r:id="rId8"/>
-    <hyperlink ref="F10" r:id="rId9"/>
-    <hyperlink ref="F11" r:id="rId10"/>
-    <hyperlink ref="F12" r:id="rId11"/>
-    <hyperlink ref="F13" r:id="rId12"/>
-    <hyperlink ref="F14" r:id="rId13"/>
-    <hyperlink ref="F15" r:id="rId14"/>
-    <hyperlink ref="F16" r:id="rId15"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5457,178 +5106,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>355</v>
+        <v>339</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>356</v>
+        <v>340</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>357</v>
+        <v>341</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B2" s="3">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>358</v>
+        <v>342</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>323</v>
+        <v>343</v>
       </c>
       <c r="B3" s="3">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>359</v>
+        <v>344</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="B4" s="3">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>360</v>
+        <v>346</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>361</v>
+        <v>307</v>
       </c>
       <c r="B5" s="3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>362</v>
+        <v>347</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>272</v>
+        <v>261</v>
       </c>
       <c r="B6" s="3">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>363</v>
+        <v>348</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>364</v>
+        <v>349</v>
       </c>
       <c r="B7" s="3">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>365</v>
+        <v>350</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>329</v>
+        <v>351</v>
       </c>
       <c r="B8" s="3">
         <v>20</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>366</v>
+        <v>352</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>367</v>
+        <v>227</v>
       </c>
       <c r="B9" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>368</v>
+        <v>353</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>236</v>
+        <v>303</v>
       </c>
       <c r="B10" s="3">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>369</v>
+        <v>354</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>370</v>
+        <v>355</v>
       </c>
       <c r="B11" s="3">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>371</v>
+        <v>356</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>372</v>
+        <v>312</v>
       </c>
       <c r="B12" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>373</v>
+        <v>357</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>374</v>
+        <v>358</v>
       </c>
       <c r="B13" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>375</v>
+        <v>359</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>230</v>
+        <v>360</v>
       </c>
       <c r="B14" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>376</v>
+        <v>361</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>377</v>
+        <v>362</v>
       </c>
       <c r="B15" s="3">
         <v>6</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>378</v>
+        <v>363</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>379</v>
+        <v>364</v>
       </c>
       <c r="B16" s="3">
         <v>6</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>380</v>
+        <v>365</v>
       </c>
     </row>
   </sheetData>
@@ -5645,13 +5294,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>381</v>
+        <v>366</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>382</v>
+        <v>367</v>
       </c>
     </row>
     <row r="2">
@@ -5659,10 +5308,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>383</v>
+        <v>368</v>
       </c>
     </row>
     <row r="3">
@@ -5670,10 +5319,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>384</v>
+        <v>369</v>
       </c>
     </row>
     <row r="4">
@@ -5681,10 +5330,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>385</v>
+        <v>370</v>
       </c>
     </row>
     <row r="5">
@@ -5695,7 +5344,18 @@
         <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>386</v>
+        <v>371</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="3">
+        <v>1</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>372</v>
       </c>
     </row>
   </sheetData>
@@ -5713,51 +5373,51 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>387</v>
+        <v>373</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>388</v>
+        <v>374</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>389</v>
+        <v>375</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B2" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>390</v>
+        <v>337</v>
       </c>
       <c r="D2" s="3"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B3" s="3">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>390</v>
+        <v>337</v>
       </c>
       <c r="D3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B4" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>390</v>
+        <v>337</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W27.xlsx
+++ b/reports/devops-juniors-israel-2026-W27.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="376">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="345">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-01T10:08:50</t>
+    <t xml:space="preserve">2026-07-02T09:30:40</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -148,6 +148,24 @@
     <t xml:space="preserve">First Seen</t>
   </si>
   <si>
+    <t xml:space="preserve">Junior IT DevOps Engineer - Temporary Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-devops-engineer-temporary-position-at-mobileye-4417802849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-25</t>
+  </si>
+  <si>
     <t xml:space="preserve">Junior AI SRE Developer</t>
   </si>
   <si>
@@ -166,24 +184,6 @@
     <t xml:space="preserve">2026-06-02</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior IT DevOps Engineer - Temporary Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobileye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-devops-engineer-temporary-position-at-mobileye-4417802849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-25</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux System Administrator</t>
   </si>
   <si>
@@ -217,643 +217,613 @@
     <t xml:space="preserve">2026-06-30</t>
   </si>
   <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voyager Labs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-voyager-labs-4420475324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Kubernetes, Terraform/IaC, Networking, Virtualization, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-sela-4428931319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-ai-4430612805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-4433428247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Inclined Systems Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SB0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-inclined-systems-engineer-at-sb0-4429860196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer 241123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-241123-at-experis-israel-4432336498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computer System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camtek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IOT student tester</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Motorola Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/iot-student-tester-at-motorola-solutions-4434451222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator – Advanced Data Center and AI Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-4428415454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-ai-4427315937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator &amp; IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inManage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eToro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-etoro-4434952696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmit Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-transmit-security-4409875183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Corp System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payoneer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.payoneer.com/careers/position/7916835/?gh_jid=7916835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Operations &amp; Helpdesk Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claroty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-helpdesk-engineer-at-claroty-4412805136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-14</t>
+  </si>
+  <si>
     <t xml:space="preserve">System Engineer</t>
   </si>
   <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashdod, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Kubernetes, Networking, Virtualization, Active Directory, Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-sqlink-group-4431944036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk and System Administrator (Israel)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Terraform/IaC, Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-and-system-administrator-israel-at-zota-4431223683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Droxi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-operations-engineer-at-droxi-4426788584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Help Desk (student position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LiveU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-student-position-at-liveu-4434277505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Korentec Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-yael-korentec-technologies-4431373486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4430443104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Desktop Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zensar Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-at-zensar-technologies-4418821535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Service Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-at-nebius-4425236974</t>
   </si>
   <si>
     <t xml:space="preserve">2026-06-12</t>
   </si>
   <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Kubernetes, Terraform/IaC, Networking, Virtualization, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-sela-4428931319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Inclined Systems Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SB0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-inclined-systems-engineer-at-sb0-4429860196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-4433428247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-ai-4430612805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peak Innovation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, Cloud (any), Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-peak-innovation-4431041046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator – Advanced Data Center and AI Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-ai-4427315937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator &amp; IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inManage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eToro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-etoro-4434952696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmit Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-transmit-security-4409875183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Corp System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Payoneer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.payoneer.com/careers/position/7916835/?gh_jid=7916835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-at-paragon-4417886377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Operations &amp; Helpdesk Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claroty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-helpdesk-engineer-at-claroty-4412805136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashdod, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Kubernetes, Networking, Virtualization, Active Directory, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-sqlink-group-4431944036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk and System Administrator (Israel)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Terraform/IaC, Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-and-system-administrator-israel-at-zota-4431223683</t>
+    <t xml:space="preserve">AMAREL LTD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-amarel-ltd-4428035454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-technician-at-nda-4428256786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riverside</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-riverside-4409620033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer (R&amp;D Environments)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-r-d-environments-at-abra-4434113221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Bootcamp Course</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-at-abra-4432200564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avionics Systems Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/avionics-systems-engineering-student-at-elbit-systems-israel-4412574130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student for Strength and Dynamics Analysis team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-for-strength-and-dynamics-analysis-team-at-elbit-systems-israel-4421930557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-liveu-4429912440</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
   </si>
   <si>
     <t xml:space="preserve">Help Desk Specialist</t>
   </si>
   <si>
-    <t xml:space="preserve">MyHeritage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-myheritage-4434704007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Help Desk (student position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LiveU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-student-position-at-liveu-4434277505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-29</t>
+    <t xml:space="preserve">Tata Consultancy Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-tata-consultancy-services-4430592021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Support Representative</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weizmann Institute of Science</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-representative-at-weizmann-institute-of-science-4431080100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helpdesk Specialist &amp; System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">365Scores</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/helpdesk-specialist-system-administrator-at-365scores-4431701042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4425017778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wobi Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-junior-at-wobi-ltd-4419670684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-21</t>
   </si>
   <si>
     <t xml:space="preserve">IT Support Specialist</t>
   </si>
   <si>
-    <t xml:space="preserve">Innoviz Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-innoviz-technologies-4407119527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spinomenal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-spinomenal-4431228721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check Point Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Cloud (any), Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-administrator-at-check-point-software-4427626178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Korentec Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-yael-korentec-technologies-4431373486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4430443104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Desktop Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zensar Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-at-zensar-technologies-4418821535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Service Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silverfort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-desk-specialist-at-silverfort-4434301874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Service Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMAREL LTD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-amarel-ltd-4428035454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riverside</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-riverside-4409620033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk &amp; IT Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mize</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-it-administrator-at-mize-4425999700</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4431915164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk (24892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-24892-at-yael-group-4427354216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nova Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-nova-ltd-4413884631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Bootcamp Course</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Git</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-at-abra-4432200564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student for Strength and Dynamics Analysis team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-for-strength-and-dynamics-analysis-team-at-elbit-systems-israel-4421930557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tata Consultancy Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-tata-consultancy-services-4430592021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk (Temporary)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Personetics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-temporary-at-personetics-4428653392</t>
+    <t xml:space="preserve">Firon Law Firm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-firon-law-firm-4435571799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician (Part-Time)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential Careers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-part-time-at-confidential-careers-4425768937</t>
   </si>
   <si>
     <t xml:space="preserve">2026-06-15</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Helpdesk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vectorious Medical Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-vectorious-medical-technologies-4434451066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">איש/אשת Help Desk Tier 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Webox LTD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%90%D7%99%D7%A9-%D7%90%D7%A9%D7%AA-help-desk-tier-1-at-webox-ltd-4430232360</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RealPlay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helpdesk Specialist &amp; System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">365Scores</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/helpdesk-specialist-system-administrator-at-365scores-4431701042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Support Representative</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weizmann Institute of Science</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-representative-at-weizmann-institute-of-science-4431080100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Infrastructure &amp; Support Specialist (Tier 2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moveo Source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-support-specialist-tier-2-at-moveo-source-4434338174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4425017778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wobi Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-junior-at-wobi-ltd-4419670684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician (Part-Time)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential Careers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-part-time-at-confidential-careers-4425768937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-sqlink-group-4429856103</t>
+    <t xml:space="preserve">IT Support Specialist (28516)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-28516-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4435800770</t>
   </si>
   <si>
     <t xml:space="preserve">Log-On Software</t>
@@ -862,286 +832,223 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-log-on-software-4432333769</t>
   </si>
   <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zoho</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-zoho-4427961067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AudioCodes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4395665709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WSC Sports</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-wsc-sports-4415703367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-abra-4423876931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist (Part time )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvei</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-part-time-at-nuvei-4421067573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aeronautical Information Service Cadet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grenada Airports Authority</t>
-  </si>
-  <si>
-    <t xml:space="preserve">St. George's,</t>
+    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI/Systems Engineer: Offensive Cybersecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UR Tech Jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-systems-engineer-offensive-cybersecurity-at-ur-tech-jobs-4425560386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Analyst (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-analyst-student-position-at-confidential-4429852518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bulwarx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-bulwarx-4435101187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">טכנאי/ת Help desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4410001855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oktopost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-oktopost-4431366669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Customer Support Helpdesk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Empathy Talent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">California, California, United States</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-customer-support-helpdesk-specialist-empathy-talent-1134244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Customer Support Technician Helpdesk Offboardings &amp;amp; Access</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pixel Machinery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-customer-support-technician-helpdesk-offboardings-amp-access-pixel-machinery-1134154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medical System Implementor Student (Part-Time, Temporary)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shavit Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/medical-system-implementor-student-part-time-temporary-at-shavit-software-4433076878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roles requiring it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What to learn / where to start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
   </si>
   <si>
     <t xml:space="preserve">Monitoring</t>
   </si>
   <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-aeronautical-information-service-cadet-grenada-airports-authority-1134169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">תומך/ת Help Desk וטכנאי/ת PC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Accel Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%AA%D7%95%D7%9E%D7%9A-%D7%AA-help-desk%C2%A0%D7%95%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-pc-at-accel-solutions-4431094783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">טכנאי/ת Help desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4410001855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Service Desk Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-desk-operator-at-tata-consultancy-services-4427424594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M.D. Mechanical Devices Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-m-d-mechanical-devices-ltd-4420118096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oktopost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-oktopost-4431366669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Customer Support Helpdesk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Empathy Talent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">California, California, United States</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-customer-support-helpdesk-specialist-empathy-talent-1134244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Customer Support Technician Helpdesk Offboardings &amp;amp; Access</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pixel Machinery</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-customer-support-technician-helpdesk-offboardings-amp-access-pixel-machinery-1134154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineering-student-at-elbit-systems-israel-4414854587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plarium</t>
+    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pivot path advice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tier 1/2 → SysAdmin → Junior DevOps. ~24 month path.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Already in IT — strengthen Linux + automation → apply to DevOps in 12-18mo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cyclical — surge after bootcamp graduations (Aug/Feb).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Often paired with on-call. Strong learning track.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Direct DevOps role — apply aggressively. Rare and competitive.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Error</t>
   </si>
   <si>
     <t xml:space="preserve">yes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-administrator-at-plarium-4431096159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roles requiring it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What to learn / where to start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pivot path advice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tier 1/2 → SysAdmin → Junior DevOps. ~24 month path.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Already in IT — strengthen Linux + automation → apply to DevOps in 12-18mo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cyclical — surge after bootcamp graduations (Aug/Feb).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Often paired with on-call. Strong learning track.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Direct DevOps role — apply aggressively. Rare and competitive.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Error</t>
   </si>
 </sst>
 </file>
@@ -1266,7 +1173,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>69</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7">
@@ -1290,7 +1197,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>369</v>
+        <v>377</v>
       </c>
     </row>
     <row r="10">
@@ -1372,7 +1279,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>45</v>
+        <v>31</v>
       </c>
     </row>
     <row r="22">
@@ -1380,7 +1287,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23">
@@ -1388,7 +1295,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
@@ -1422,7 +1329,7 @@
         <v>31</v>
       </c>
       <c r="B28" s="3">
-        <v>62</v>
+        <v>52</v>
       </c>
     </row>
     <row r="29">
@@ -1430,7 +1337,7 @@
         <v>32</v>
       </c>
       <c r="B29" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30">
@@ -1438,7 +1345,7 @@
         <v>33</v>
       </c>
       <c r="B30" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -1506,7 +1413,7 @@
         <v>46</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
@@ -1538,7 +1445,7 @@
         <v>52</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
@@ -1567,7 +1474,7 @@
         <v>57</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>26</v>
@@ -1634,10 +1541,10 @@
         <v>69</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F6" s="3">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>70</v>
@@ -1695,7 +1602,7 @@
         <v>79</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>26</v>
@@ -1704,16 +1611,16 @@
         <v>76</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9">
@@ -1721,13 +1628,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>26</v>
@@ -1736,7 +1643,7 @@
         <v>76</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>31</v>
@@ -1745,7 +1652,7 @@
         <v>86</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10">
@@ -1753,7 +1660,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>88</v>
@@ -1768,16 +1675,16 @@
         <v>76</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11">
@@ -1785,31 +1692,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F11" s="3">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12">
@@ -1817,31 +1724,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F12" s="3">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>66</v>
+        <v>102</v>
       </c>
     </row>
     <row r="13">
@@ -1849,31 +1756,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F13" s="3">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14">
@@ -1881,31 +1788,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F14" s="3">
         <v>52</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>66</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15">
@@ -1913,31 +1820,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>108</v>
+        <v>84</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F15" s="3">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>112</v>
+        <v>77</v>
       </c>
     </row>
     <row r="16">
@@ -1945,31 +1852,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="D16" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F16" s="3">
+        <v>52</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="E16" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F16" s="3">
-        <v>47</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>115</v>
-      </c>
       <c r="H16" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>116</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>95</v>
+        <v>117</v>
       </c>
     </row>
     <row r="17">
@@ -1977,31 +1884,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F17" s="3">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>119</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18">
@@ -2009,31 +1916,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>46</v>
+        <v>124</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F18" s="3">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="19">
@@ -2041,31 +1948,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>68</v>
+        <v>128</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>69</v>
+        <v>129</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F19" s="3">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>49</v>
+        <v>102</v>
       </c>
     </row>
     <row r="20">
@@ -2073,19 +1980,19 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F20" s="3">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>130</v>
@@ -2094,10 +2001,10 @@
         <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="21">
@@ -2105,31 +2012,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>67</v>
+        <v>135</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>134</v>
+        <v>52</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F21" s="3">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>112</v>
+        <v>139</v>
       </c>
     </row>
     <row r="22">
@@ -2137,31 +2044,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F22" s="3">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>77</v>
+        <v>144</v>
       </c>
     </row>
     <row r="23">
@@ -2169,31 +2076,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F23" s="3">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>66</v>
+        <v>127</v>
       </c>
     </row>
     <row r="24">
@@ -2201,31 +2108,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>148</v>
+        <v>89</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F24" s="3">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>151</v>
+        <v>77</v>
       </c>
     </row>
     <row r="25">
@@ -2233,31 +2140,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F25" s="3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="26">
@@ -2265,13 +2172,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>109</v>
+        <v>162</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>25</v>
@@ -2280,16 +2187,16 @@
         <v>30</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>77</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>
@@ -2328,8 +2235,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="33" customWidth="1"/>
-    <col min="3" max="3" width="44" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="3" width="47" customWidth="1"/>
     <col min="4" max="4" width="31" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -2342,7 +2249,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>36</v>
@@ -2357,22 +2264,22 @@
         <v>39</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>41</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>43</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
     </row>
     <row r="2">
@@ -2386,7 +2293,7 @@
         <v>46</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E2" s="3">
         <v>100</v>
@@ -2395,7 +2302,7 @@
         <v>47</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>31</v>
@@ -2407,7 +2314,7 @@
         <v>49</v>
       </c>
       <c r="K2" s="3">
-        <v>29</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3">
@@ -2421,7 +2328,7 @@
         <v>52</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E3" s="3">
         <v>100</v>
@@ -2430,7 +2337,7 @@
         <v>53</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>31</v>
@@ -2442,7 +2349,7 @@
         <v>55</v>
       </c>
       <c r="K3" s="3">
-        <v>37</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
@@ -2453,7 +2360,7 @@
         <v>57</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>26</v>
@@ -2465,7 +2372,7 @@
         <v>58</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>31</v>
@@ -2477,7 +2384,7 @@
         <v>60</v>
       </c>
       <c r="K4" s="3">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5">
@@ -2500,7 +2407,7 @@
         <v>64</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>31</v>
@@ -2512,7 +2419,7 @@
         <v>66</v>
       </c>
       <c r="K5" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -2526,16 +2433,16 @@
         <v>69</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E6" s="3">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>70</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>31</v>
@@ -2547,7 +2454,7 @@
         <v>72</v>
       </c>
       <c r="K6" s="3">
-        <v>19</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7">
@@ -2570,7 +2477,7 @@
         <v>75</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>31</v>
@@ -2582,7 +2489,7 @@
         <v>77</v>
       </c>
       <c r="K7" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -2593,7 +2500,7 @@
         <v>79</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>26</v>
@@ -2602,33 +2509,33 @@
         <v>76</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="K8" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>26</v>
@@ -2637,10 +2544,10 @@
         <v>76</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>31</v>
@@ -2649,15 +2556,15 @@
         <v>86</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="K9" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>88</v>
@@ -2672,474 +2579,474 @@
         <v>76</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="K10" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E11" s="3">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="K11" s="3">
-        <v>47</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E12" s="3">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>66</v>
+        <v>102</v>
       </c>
       <c r="K12" s="3">
-        <v>1</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E13" s="3">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="K13" s="3">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E14" s="3">
         <v>52</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>66</v>
+        <v>112</v>
       </c>
       <c r="K14" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>108</v>
+        <v>84</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E15" s="3">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="C16" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" s="3">
+        <v>52</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E16" s="3">
-        <v>47</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>115</v>
-      </c>
       <c r="G16" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>116</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="K16" s="3">
-        <v>47</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E17" s="3">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>119</v>
+        <v>66</v>
       </c>
       <c r="K17" s="3">
-        <v>30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>46</v>
+        <v>124</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E18" s="3">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="K18" s="3">
-        <v>43</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>68</v>
+        <v>128</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>69</v>
+        <v>129</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E19" s="3">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>49</v>
+        <v>102</v>
       </c>
       <c r="K19" s="3">
-        <v>29</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E20" s="3">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>130</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="K20" s="3">
-        <v>17</v>
+        <v>31</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>67</v>
+        <v>135</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>134</v>
+        <v>52</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E21" s="3">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>112</v>
+        <v>139</v>
       </c>
       <c r="K21" s="3">
-        <v>0</v>
+        <v>44</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E22" s="3">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>77</v>
+        <v>144</v>
       </c>
       <c r="K22" s="3">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E23" s="3">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>66</v>
+        <v>127</v>
       </c>
       <c r="K23" s="3">
         <v>1</v>
@@ -3147,83 +3054,83 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>148</v>
+        <v>89</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E24" s="3">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>151</v>
+        <v>77</v>
       </c>
       <c r="K24" s="3">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E25" s="3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="K25" s="3">
-        <v>31</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>109</v>
+        <v>162</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>25</v>
@@ -3232,57 +3139,57 @@
         <v>30</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="K26" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E27" s="3">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>72</v>
+        <v>175</v>
       </c>
       <c r="K27" s="3">
-        <v>19</v>
+        <v>43</v>
       </c>
     </row>
     <row r="28">
@@ -3290,7 +3197,7 @@
         <v>56</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>63</v>
@@ -3302,33 +3209,33 @@
         <v>28</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="K28" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>25</v>
@@ -3337,33 +3244,33 @@
         <v>27</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="K29" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>25</v>
@@ -3372,30 +3279,30 @@
         <v>27</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>157</v>
+        <v>190</v>
       </c>
       <c r="K30" s="3">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>74</v>
@@ -3407,68 +3314,68 @@
         <v>24</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="K31" s="3">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>69</v>
+        <v>197</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E32" s="3">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="K32" s="3">
-        <v>0</v>
+        <v>48</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>25</v>
@@ -3477,30 +3384,30 @@
         <v>20</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>95</v>
+        <v>205</v>
       </c>
       <c r="K33" s="3">
-        <v>47</v>
+        <v>20</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>63</v>
@@ -3512,33 +3419,33 @@
         <v>20</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="K34" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>107</v>
+        <v>209</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>69</v>
+        <v>211</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>25</v>
@@ -3547,33 +3454,33 @@
         <v>20</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="K35" s="3">
-        <v>47</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>204</v>
+        <v>122</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>25</v>
@@ -3582,54 +3489,54 @@
         <v>20</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>208</v>
+        <v>102</v>
       </c>
       <c r="K36" s="3">
-        <v>21</v>
+        <v>48</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>210</v>
+        <v>192</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>211</v>
+        <v>74</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E37" s="3">
         <v>17</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="K37" s="3">
         <v>0</v>
@@ -3637,83 +3544,83 @@
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>215</v>
+        <v>192</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>148</v>
+        <v>221</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E38" s="3">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>179</v>
+        <v>224</v>
       </c>
       <c r="K38" s="3">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>67</v>
+        <v>225</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>219</v>
+        <v>202</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E39" s="3">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>212</v>
+        <v>227</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="K39" s="3">
-        <v>47</v>
+        <v>39</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>186</v>
+        <v>226</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>27</v>
@@ -3722,68 +3629,68 @@
         <v>13</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H40" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="K40" s="3">
-        <v>8</v>
+        <v>24</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>226</v>
+        <v>67</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>210</v>
+        <v>161</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>211</v>
+        <v>162</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E41" s="3">
         <v>13</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>229</v>
+        <v>184</v>
       </c>
       <c r="K41" s="3">
-        <v>23</v>
+        <v>14</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>25</v>
@@ -3792,33 +3699,33 @@
         <v>10</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="J42" s="3" t="s">
         <v>60</v>
       </c>
       <c r="K42" s="3">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>141</v>
+        <v>240</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>25</v>
@@ -3827,33 +3734,33 @@
         <v>10</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="K43" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>25</v>
@@ -3862,33 +3769,33 @@
         <v>10</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>243</v>
+        <v>112</v>
       </c>
       <c r="K44" s="3">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>246</v>
+        <v>89</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>25</v>
@@ -3897,124 +3804,124 @@
         <v>10</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="K45" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>249</v>
+        <v>192</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E46" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>252</v>
+        <v>232</v>
       </c>
       <c r="K46" s="3">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>107</v>
+        <v>255</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>69</v>
+        <v>124</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E47" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>60</v>
+        <v>259</v>
       </c>
       <c r="K47" s="3">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>69</v>
+        <v>211</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E48" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>236</v>
+        <v>253</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="K48" s="3">
         <v>0</v>
@@ -4022,69 +3929,69 @@
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>219</v>
+        <v>74</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E49" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>151</v>
+        <v>266</v>
       </c>
       <c r="K49" s="3">
-        <v>2</v>
+        <v>17</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>265</v>
+        <v>74</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E50" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>233</v>
+        <v>253</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="K50" s="3">
         <v>0</v>
@@ -4092,10 +3999,10 @@
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>267</v>
+        <v>240</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>186</v>
+        <v>270</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>74</v>
@@ -4107,124 +4014,124 @@
         <v>6</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>268</v>
+        <v>253</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>229</v>
+        <v>127</v>
       </c>
       <c r="K51" s="3">
-        <v>23</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>109</v>
+        <v>274</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E52" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>274</v>
+        <v>97</v>
       </c>
       <c r="K52" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>74</v>
+        <v>187</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E53" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H53" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>243</v>
+        <v>281</v>
       </c>
       <c r="K53" s="3">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>141</v>
+        <v>282</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>133</v>
+        <v>283</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>143</v>
+        <v>211</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E54" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>77</v>
+        <v>286</v>
       </c>
       <c r="K54" s="3">
         <v>7</v>
@@ -4232,34 +4139,34 @@
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>141</v>
+        <v>287</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>74</v>
+        <v>221</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E55" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>268</v>
+        <v>289</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="K55" s="3">
         <v>0</v>
@@ -4267,527 +4174,179 @@
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>246</v>
+        <v>69</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E56" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H56" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>132</v>
+        <v>295</v>
       </c>
       <c r="K56" s="3">
-        <v>17</v>
+        <v>37</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>286</v>
+        <v>260</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E57" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>268</v>
+        <v>289</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="K57" s="3">
-        <v>38</v>
+        <v>8</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>244</v>
+        <v>298</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E58" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>157</v>
+        <v>66</v>
       </c>
       <c r="K58" s="3">
-        <v>31</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>186</v>
+        <v>303</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>74</v>
+        <v>300</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E59" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>295</v>
+        <v>83</v>
       </c>
       <c r="K59" s="3">
-        <v>28</v>
+        <v>4</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>69</v>
+        <v>211</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E60" s="3">
-        <v>6</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>268</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F60" s="3"/>
       <c r="G60" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>299</v>
+        <v>112</v>
       </c>
       <c r="K60" s="3">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E61" s="3">
-        <v>4</v>
-      </c>
-      <c r="F61" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="G61" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H61" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I61" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="J61" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="K61" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="D62" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E62" s="3">
-        <v>3</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="K62" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E63" s="3">
-        <v>3</v>
-      </c>
-      <c r="F63" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="G63" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H63" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I63" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="J63" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="K63" s="3">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="D64" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E64" s="3">
-        <v>3</v>
-      </c>
-      <c r="F64" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="G64" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H64" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I64" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="J64" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="K64" s="3">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="D65" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E65" s="3">
-        <v>3</v>
-      </c>
-      <c r="F65" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="G65" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H65" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I65" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="J65" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="K65" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="D66" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E66" s="3">
-        <v>3</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="K66" s="3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E67" s="3">
-        <v>3</v>
-      </c>
-      <c r="F67" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="G67" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H67" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I67" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="J67" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="K67" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="D68" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E68" s="3">
-        <v>3</v>
-      </c>
-      <c r="F68" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="G68" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H68" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I68" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="J68" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="K68" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="D69" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E69" s="3">
-        <v>0</v>
-      </c>
-      <c r="F69" s="3"/>
-      <c r="G69" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H69" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I69" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="J69" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="K69" s="3">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D70" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E70" s="3">
-        <v>0</v>
-      </c>
-      <c r="F70" s="3"/>
-      <c r="G70" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="H70" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I70" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="J70" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="K70" s="3">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:K70"/>
+  <autoFilter ref="A1:K60"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -4848,16 +4407,6 @@
     <hyperlink ref="I58" r:id="rId57"/>
     <hyperlink ref="I59" r:id="rId58"/>
     <hyperlink ref="I60" r:id="rId59"/>
-    <hyperlink ref="I61" r:id="rId60"/>
-    <hyperlink ref="I62" r:id="rId61"/>
-    <hyperlink ref="I63" r:id="rId62"/>
-    <hyperlink ref="I64" r:id="rId63"/>
-    <hyperlink ref="I65" r:id="rId64"/>
-    <hyperlink ref="I66" r:id="rId65"/>
-    <hyperlink ref="I67" r:id="rId66"/>
-    <hyperlink ref="I68" r:id="rId67"/>
-    <hyperlink ref="I69" r:id="rId68"/>
-    <hyperlink ref="I70" r:id="rId69"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4865,8 +4414,8 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="49" customWidth="1"/>
-    <col min="2" max="2" width="33" customWidth="1"/>
+    <col min="1" max="1" width="47" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="25" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
@@ -4888,10 +4437,10 @@
         <v>39</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>43</v>
@@ -4899,186 +4448,186 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D2" s="3">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>67</v>
+        <v>103</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>133</v>
+        <v>104</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>26</v>
       </c>
       <c r="D3" s="3">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>135</v>
+        <v>106</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>136</v>
+        <v>107</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>189</v>
+        <v>209</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D4" s="3">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>191</v>
+        <v>212</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>192</v>
+        <v>213</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>210</v>
+        <v>192</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D5" s="3">
         <v>17</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>244</v>
+        <v>260</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>245</v>
+        <v>261</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D6" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>236</v>
+        <v>253</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>247</v>
+        <v>262</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D7" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>236</v>
+        <v>253</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D8" s="3">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>233</v>
+        <v>275</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>141</v>
+        <v>287</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D9" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>268</v>
+        <v>289</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -5106,178 +4655,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>339</v>
+        <v>308</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>340</v>
+        <v>309</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>341</v>
+        <v>310</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>317</v>
+        <v>289</v>
       </c>
       <c r="B2" s="3">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>342</v>
+        <v>311</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>343</v>
+        <v>284</v>
       </c>
       <c r="B3" s="3">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>344</v>
+        <v>312</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>345</v>
+        <v>247</v>
       </c>
       <c r="B4" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>346</v>
+        <v>313</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="B5" s="3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>347</v>
+        <v>315</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="B6" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>348</v>
+        <v>316</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>349</v>
+        <v>275</v>
       </c>
       <c r="B7" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>350</v>
+        <v>317</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>351</v>
+        <v>227</v>
       </c>
       <c r="B8" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>227</v>
+        <v>319</v>
       </c>
       <c r="B9" s="3">
         <v>18</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>353</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>303</v>
+        <v>321</v>
       </c>
       <c r="B10" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>354</v>
+        <v>322</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>355</v>
+        <v>323</v>
       </c>
       <c r="B11" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>312</v>
+        <v>293</v>
       </c>
       <c r="B12" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>357</v>
+        <v>325</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>358</v>
+        <v>326</v>
       </c>
       <c r="B13" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>359</v>
+        <v>327</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>360</v>
+        <v>328</v>
       </c>
       <c r="B14" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>361</v>
+        <v>329</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>362</v>
+        <v>330</v>
       </c>
       <c r="B15" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>363</v>
+        <v>331</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>364</v>
+        <v>332</v>
       </c>
       <c r="B16" s="3">
         <v>6</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>365</v>
+        <v>333</v>
       </c>
     </row>
   </sheetData>
@@ -5297,10 +4846,10 @@
         <v>38</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>366</v>
+        <v>334</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>367</v>
+        <v>335</v>
       </c>
     </row>
     <row r="2">
@@ -5308,10 +4857,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>368</v>
+        <v>336</v>
       </c>
     </row>
     <row r="3">
@@ -5319,10 +4868,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>369</v>
+        <v>337</v>
       </c>
     </row>
     <row r="4">
@@ -5330,10 +4879,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>370</v>
+        <v>338</v>
       </c>
     </row>
     <row r="5">
@@ -5344,7 +4893,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>371</v>
+        <v>339</v>
       </c>
     </row>
     <row r="6">
@@ -5355,7 +4904,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>372</v>
+        <v>340</v>
       </c>
     </row>
   </sheetData>
@@ -5376,13 +4925,13 @@
         <v>41</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>373</v>
+        <v>341</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>374</v>
+        <v>342</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>375</v>
+        <v>343</v>
       </c>
     </row>
     <row r="2">
@@ -5390,10 +4939,10 @@
         <v>32</v>
       </c>
       <c r="B2" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -5402,10 +4951,10 @@
         <v>31</v>
       </c>
       <c r="B3" s="3">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="D3" s="3"/>
     </row>
@@ -5414,10 +4963,10 @@
         <v>33</v>
       </c>
       <c r="B4" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W27.xlsx
+++ b/reports/devops-juniors-israel-2026-W27.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="379">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-02T09:30:40</t>
+    <t xml:space="preserve">2026-07-03T09:33:36</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -250,745 +250,847 @@
     <t xml:space="preserve">2026-06-24</t>
   </si>
   <si>
+    <t xml:space="preserve">AI Inclined Systems Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SB0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-inclined-systems-engineer-at-sb0-4429860196</t>
+  </si>
+  <si>
     <t xml:space="preserve">System Administrator</t>
   </si>
   <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-4433428247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-28</t>
+  </si>
+  <si>
     <t xml:space="preserve">NVIDIA AI</t>
   </si>
   <si>
     <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-ai-4430612805</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-06-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-4433428247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Inclined Systems Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SB0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-inclined-systems-engineer-at-sb0-4429860196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer 241123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-241123-at-experis-israel-4432336498</t>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eToro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-etoro-4434952696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmit Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-transmit-security-4409875183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Corp System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payoneer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.payoneer.com/careers/position/7916835/?gh_jid=7916835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Operations &amp; Helpdesk Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claroty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-helpdesk-engineer-at-claroty-4412805136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-at-paragon-4417886377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer - Intern position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Align Technology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Cloud (any), Monitoring, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-intern-position-at-align-technology-4303646784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashdod, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Kubernetes, Networking, Virtualization, Active Directory, Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-sqlink-group-4431944036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MyHeritage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-myheritage-4434704007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk and System Administrator (Israel)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Terraform/IaC, Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-and-system-administrator-israel-at-zota-4431223683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Help Desk (student position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LiveU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-student-position-at-liveu-4434277505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spinomenal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-spinomenal-4431228721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check Point Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Cloud (any), Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-administrator-at-check-point-software-4427626178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Innoviz Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-innoviz-technologies-4407119527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Korentec Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-yael-korentec-technologies-4431373486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4430443104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Desktop Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zensar Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-at-zensar-technologies-4418821535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logica-IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-desk-technician-at-logica-it-4432768849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silverfort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-desk-specialist-at-silverfort-4434301874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Service Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riverside</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-riverside-4409620033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-technician-at-commit-4435577338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-at-nebius-4425236974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4431915164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avionics Systems Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/avionics-systems-engineering-student-at-elbit-systems-israel-4412574130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">טכנאי/ת Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4427161897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-liveu-4429912440</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Support Representative</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weizmann Institute of Science</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-representative-at-weizmann-institute-of-science-4431080100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helpdesk Specialist &amp; System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">365Scores</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/helpdesk-specialist-system-administrator-at-365scores-4431701042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Field IT Technician (36179)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/field-it-technician-36179-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4435810222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tata Consultancy Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-tata-consultancy-services-4430592021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk (Temporary)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personetics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-temporary-at-personetics-4428653392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vectorious Medical Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-vectorious-medical-technologies-4434451066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RealPlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support – Power Quality Meters &amp; Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elspec Engineering ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-%E2%80%93-power-quality-meters-software-at-elspec-engineering-ltd-4413397801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AudioCodes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4395665709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-abra-4423876931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WSC Sports</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-wsc-sports-4415703367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Log-On Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-log-on-software-4432333769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist (28516)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-28516-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4435800770</t>
   </si>
   <si>
     <t xml:space="preserve">2026-07-02</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Computer System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Camtek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IOT student tester</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Motorola Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/iot-student-tester-at-motorola-solutions-4434451222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator – Advanced Data Center and AI Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-4428415454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-ai-4427315937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator &amp; IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inManage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eToro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-etoro-4434952696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmit Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-transmit-security-4409875183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Corp System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Payoneer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.payoneer.com/careers/position/7916835/?gh_jid=7916835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Operations &amp; Helpdesk Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claroty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-helpdesk-engineer-at-claroty-4412805136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashdod, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Kubernetes, Networking, Virtualization, Active Directory, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-sqlink-group-4431944036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk and System Administrator (Israel)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Terraform/IaC, Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-and-system-administrator-israel-at-zota-4431223683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Droxi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-operations-engineer-at-droxi-4426788584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Help Desk (student position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LiveU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-student-position-at-liveu-4434277505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Korentec Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-yael-korentec-technologies-4431373486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4430443104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Desktop Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zensar Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-at-zensar-technologies-4418821535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Service Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nebius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-at-nebius-4425236974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMAREL LTD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-amarel-ltd-4428035454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-technician-at-nda-4428256786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riverside</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-riverside-4409620033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer (R&amp;D Environments)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-r-d-environments-at-abra-4434113221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Bootcamp Course</t>
+    <t xml:space="preserve">Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4425017778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician (Part-Time)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential Careers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-part-time-at-confidential-careers-4425768937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wobi Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-junior-at-wobi-ltd-4419670684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SuperPlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-superplay-4436326306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Firon Law Firm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-firon-law-firm-4435571799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zoho</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-zoho-4427961067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multimedia Systems &amp; IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deloitte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/multimedia-systems-it-support-specialist-at-deloitte-4433302126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI/Systems Engineer: Offensive Cybersecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UR Tech Jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-systems-engineer-offensive-cybersecurity-at-ur-tech-jobs-4425560386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Analyst (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-analyst-student-position-at-confidential-4429852518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bulwarx</t>
   </si>
   <si>
     <t xml:space="preserve">Raanana, Center District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Git</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-at-abra-4432200564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avionics Systems Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/avionics-systems-engineering-student-at-elbit-systems-israel-4412574130</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student for Strength and Dynamics Analysis team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-for-strength-and-dynamics-analysis-team-at-elbit-systems-israel-4421930557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-liveu-4429912440</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tata Consultancy Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-tata-consultancy-services-4430592021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Support Representative</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weizmann Institute of Science</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-representative-at-weizmann-institute-of-science-4431080100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helpdesk Specialist &amp; System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">365Scores</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/helpdesk-specialist-system-administrator-at-365scores-4431701042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4425017778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wobi Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-junior-at-wobi-ltd-4419670684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Firon Law Firm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-firon-law-firm-4435571799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician (Part-Time)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential Careers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-part-time-at-confidential-careers-4425768937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist (28516)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-28516-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4435800770</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Log-On Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-log-on-software-4432333769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI/Systems Engineer: Offensive Cybersecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UR Tech Jobs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-systems-engineer-offensive-cybersecurity-at-ur-tech-jobs-4425560386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Analyst (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-analyst-student-position-at-confidential-4429852518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bulwarx</t>
-  </si>
-  <si>
     <t xml:space="preserve">Troubleshooting</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-bulwarx-4435101187</t>
   </si>
   <si>
-    <t xml:space="preserve">טכנאי/ת Help desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genie</t>
+    <t xml:space="preserve">Oktopost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-oktopost-4431366669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service Desk Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-desk-operator-at-tata-consultancy-services-4427424594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">תומך/ת Help Desk וטכנאי/ת PC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accel Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%AA%D7%95%D7%9E%D7%9A-%D7%AA-help-desk%C2%A0%D7%95%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-pc-at-accel-solutions-4431094783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M.D. Mechanical Devices Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-m-d-mechanical-devices-ltd-4420118096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Customer Support Helpdesk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Empathy Talent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">California, California, United States</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-customer-support-helpdesk-specialist-empathy-talent-1134244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roles requiring it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What to learn / where to start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
   </si>
   <si>
     <t xml:space="preserve">Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4410001855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oktopost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-oktopost-4431366669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Customer Support Helpdesk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Empathy Talent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">California, California, United States</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-customer-support-helpdesk-specialist-empathy-talent-1134244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Customer Support Technician Helpdesk Offboardings &amp;amp; Access</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pixel Machinery</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-customer-support-technician-helpdesk-offboardings-amp-access-pixel-machinery-1134154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medical System Implementor Student (Part-Time, Temporary)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shavit Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/medical-system-implementor-student-part-time-temporary-at-shavit-software-4433076878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roles requiring it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What to learn / where to start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
   </si>
   <si>
     <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
@@ -1173,7 +1275,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>59</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7">
@@ -1181,7 +1283,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -1189,7 +1291,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9">
@@ -1197,7 +1299,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>377</v>
+        <v>381</v>
       </c>
     </row>
     <row r="10">
@@ -1279,7 +1381,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>31</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22">
@@ -1287,7 +1389,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23">
@@ -1295,7 +1397,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -1329,7 +1431,7 @@
         <v>31</v>
       </c>
       <c r="B28" s="3">
-        <v>52</v>
+        <v>62</v>
       </c>
     </row>
     <row r="29">
@@ -1345,7 +1447,7 @@
         <v>33</v>
       </c>
       <c r="B30" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1620,7 +1722,7 @@
         <v>82</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9">
@@ -1628,7 +1730,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>84</v>
@@ -1643,16 +1745,16 @@
         <v>76</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10">
@@ -1660,13 +1762,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>26</v>
@@ -1675,7 +1777,7 @@
         <v>76</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>31</v>
@@ -1684,7 +1786,7 @@
         <v>91</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11">
@@ -1698,25 +1800,25 @@
         <v>93</v>
       </c>
       <c r="D11" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F11" s="3">
+        <v>57</v>
+      </c>
+      <c r="G11" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="E11" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F11" s="3">
-        <v>71</v>
-      </c>
-      <c r="G11" s="3" t="s">
+      <c r="H11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="H11" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I11" s="3" t="s">
+      <c r="J11" s="3" t="s">
         <v>96</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="12">
@@ -1724,19 +1826,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>89</v>
-      </c>
       <c r="E12" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F12" s="3">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>100</v>
@@ -1756,31 +1858,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="E13" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F13" s="3">
+        <v>47</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="E13" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F13" s="3">
-        <v>56</v>
-      </c>
-      <c r="G13" s="3" t="s">
+      <c r="H13" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="H13" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>107</v>
-      </c>
       <c r="J13" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14">
@@ -1788,31 +1890,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F14" s="3">
+        <v>47</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>109</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F14" s="3">
-        <v>52</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="15">
@@ -1820,31 +1922,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>84</v>
+        <v>111</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>85</v>
+        <v>52</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F15" s="3">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="G15" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="J15" s="3" t="s">
         <v>114</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="16">
@@ -1852,31 +1954,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>80</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F16" s="3">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="17">
@@ -1884,31 +1986,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F17" s="3">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -1916,31 +2018,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>124</v>
+        <v>69</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F18" s="3">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="19">
@@ -1948,28 +2050,28 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F19" s="3">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="J19" s="3" t="s">
         <v>102</v>
@@ -1980,31 +2082,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>89</v>
+        <v>136</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F20" s="3">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>134</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21">
@@ -2012,31 +2114,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F21" s="3">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>139</v>
+        <v>77</v>
       </c>
     </row>
     <row r="22">
@@ -2044,31 +2146,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>89</v>
+        <v>145</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F22" s="3">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="23">
@@ -2076,31 +2178,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>147</v>
+        <v>99</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F23" s="3">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>127</v>
+        <v>77</v>
       </c>
     </row>
     <row r="24">
@@ -2108,31 +2210,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F24" s="3">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>77</v>
+        <v>157</v>
       </c>
     </row>
     <row r="25">
@@ -2140,31 +2242,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F25" s="3">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="26">
@@ -2172,31 +2274,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>160</v>
+        <v>56</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>162</v>
+        <v>63</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F26" s="3">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>112</v>
+        <v>166</v>
       </c>
     </row>
   </sheetData>
@@ -2249,7 +2351,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>36</v>
@@ -2264,22 +2366,22 @@
         <v>39</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>41</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>43</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="2">
@@ -2302,7 +2404,7 @@
         <v>47</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>31</v>
@@ -2314,7 +2416,7 @@
         <v>49</v>
       </c>
       <c r="K2" s="3">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3">
@@ -2337,7 +2439,7 @@
         <v>53</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>31</v>
@@ -2349,7 +2451,7 @@
         <v>55</v>
       </c>
       <c r="K3" s="3">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">
@@ -2372,7 +2474,7 @@
         <v>58</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>31</v>
@@ -2384,7 +2486,7 @@
         <v>60</v>
       </c>
       <c r="K4" s="3">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5">
@@ -2407,7 +2509,7 @@
         <v>64</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>31</v>
@@ -2419,7 +2521,7 @@
         <v>66</v>
       </c>
       <c r="K5" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -2442,7 +2544,7 @@
         <v>70</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>31</v>
@@ -2454,7 +2556,7 @@
         <v>72</v>
       </c>
       <c r="K6" s="3">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7">
@@ -2477,7 +2579,7 @@
         <v>75</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>31</v>
@@ -2489,7 +2591,7 @@
         <v>77</v>
       </c>
       <c r="K7" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -2512,7 +2614,7 @@
         <v>81</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>31</v>
@@ -2521,15 +2623,15 @@
         <v>82</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="K8" s="3">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>84</v>
@@ -2544,33 +2646,33 @@
         <v>76</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="K9" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>26</v>
@@ -2579,10 +2681,10 @@
         <v>76</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>31</v>
@@ -2591,10 +2693,10 @@
         <v>91</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K10" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -2605,54 +2707,54 @@
         <v>93</v>
       </c>
       <c r="C11" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11" s="3">
+        <v>57</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E11" s="3">
-        <v>71</v>
-      </c>
-      <c r="F11" s="3" t="s">
+      <c r="G11" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="G11" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I11" s="3" t="s">
+      <c r="J11" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="J11" s="3" t="s">
-        <v>97</v>
-      </c>
       <c r="K11" s="3">
-        <v>0</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="C12" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>89</v>
-      </c>
       <c r="D12" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E12" s="3">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>100</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>31</v>
@@ -2664,505 +2766,505 @@
         <v>102</v>
       </c>
       <c r="K12" s="3">
-        <v>48</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="C13" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" s="3">
+        <v>47</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E13" s="3">
-        <v>56</v>
-      </c>
-      <c r="F13" s="3" t="s">
+      <c r="G13" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="G13" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>107</v>
-      </c>
       <c r="J13" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K13" s="3">
-        <v>0</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" s="3">
+        <v>47</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E14" s="3">
-        <v>52</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>112</v>
-      </c>
       <c r="K14" s="3">
-        <v>3</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>84</v>
+        <v>111</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>85</v>
+        <v>52</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E15" s="3">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F15" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="J15" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="G15" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>77</v>
-      </c>
       <c r="K15" s="3">
-        <v>8</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>80</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E16" s="3">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="K16" s="3">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E17" s="3">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="K17" s="3">
-        <v>2</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>124</v>
+        <v>69</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E18" s="3">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="K18" s="3">
-        <v>1</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E19" s="3">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="J19" s="3" t="s">
         <v>102</v>
       </c>
       <c r="K19" s="3">
-        <v>48</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>89</v>
+        <v>136</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E20" s="3">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>134</v>
+        <v>66</v>
       </c>
       <c r="K20" s="3">
-        <v>31</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E21" s="3">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>139</v>
+        <v>77</v>
       </c>
       <c r="K21" s="3">
-        <v>44</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>89</v>
+        <v>145</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E22" s="3">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="K22" s="3">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>147</v>
+        <v>99</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E23" s="3">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>127</v>
+        <v>77</v>
       </c>
       <c r="K23" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E24" s="3">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>77</v>
+        <v>157</v>
       </c>
       <c r="K24" s="3">
-        <v>8</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E25" s="3">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="K25" s="3">
-        <v>21</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>160</v>
+        <v>56</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>162</v>
+        <v>63</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E26" s="3">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>112</v>
+        <v>166</v>
       </c>
       <c r="K26" s="3">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>74</v>
@@ -3174,68 +3276,68 @@
         <v>28</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>175</v>
+        <v>128</v>
       </c>
       <c r="K27" s="3">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>56</v>
+        <v>177</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E28" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="K28" s="3">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>89</v>
+        <v>184</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>25</v>
@@ -3244,33 +3346,33 @@
         <v>27</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>184</v>
+        <v>162</v>
       </c>
       <c r="K29" s="3">
-        <v>14</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>187</v>
+        <v>52</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>25</v>
@@ -3279,68 +3381,68 @@
         <v>27</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="K30" s="3">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E31" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J31" s="3" t="s">
         <v>102</v>
       </c>
       <c r="K31" s="3">
-        <v>48</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>25</v>
@@ -3349,33 +3451,33 @@
         <v>20</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="K32" s="3">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>200</v>
+        <v>97</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>201</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>202</v>
+        <v>80</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>25</v>
@@ -3384,68 +3486,68 @@
         <v>20</v>
       </c>
       <c r="F33" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I33" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="G33" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>204</v>
-      </c>
       <c r="J33" s="3" t="s">
-        <v>205</v>
+        <v>96</v>
       </c>
       <c r="K33" s="3">
-        <v>20</v>
+        <v>49</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>78</v>
+        <v>204</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E34" s="3">
         <v>20</v>
       </c>
       <c r="F34" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I34" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="G34" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>208</v>
-      </c>
       <c r="J34" s="3" t="s">
-        <v>117</v>
+        <v>191</v>
       </c>
       <c r="K34" s="3">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B35" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="C35" s="3" t="s">
         <v>210</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>211</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>25</v>
@@ -3454,243 +3556,243 @@
         <v>20</v>
       </c>
       <c r="F35" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I35" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="G35" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>213</v>
-      </c>
       <c r="J35" s="3" t="s">
-        <v>97</v>
+        <v>157</v>
       </c>
       <c r="K35" s="3">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>122</v>
+        <v>213</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>214</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>89</v>
+        <v>215</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E36" s="3">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J36" s="3" t="s">
         <v>102</v>
       </c>
       <c r="K36" s="3">
-        <v>48</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>192</v>
+        <v>214</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>74</v>
+        <v>210</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E37" s="3">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>97</v>
+        <v>60</v>
       </c>
       <c r="K37" s="3">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>192</v>
+        <v>222</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>221</v>
+        <v>131</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E38" s="3">
         <v>13</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K38" s="3">
-        <v>9</v>
+        <v>22</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>225</v>
+        <v>67</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>226</v>
+        <v>144</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>202</v>
+        <v>145</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E39" s="3">
         <v>13</v>
       </c>
       <c r="F39" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I39" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="G39" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H39" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I39" s="3" t="s">
-        <v>228</v>
-      </c>
       <c r="J39" s="3" t="s">
-        <v>60</v>
+        <v>181</v>
       </c>
       <c r="K39" s="3">
-        <v>39</v>
+        <v>15</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="B40" s="3" t="s">
         <v>229</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>226</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>230</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E40" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>232</v>
+        <v>60</v>
       </c>
       <c r="K40" s="3">
-        <v>24</v>
+        <v>40</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>67</v>
+        <v>233</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>161</v>
+        <v>234</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>162</v>
+        <v>235</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E41" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>184</v>
+        <v>148</v>
       </c>
       <c r="K41" s="3">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>237</v>
+        <v>80</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>25</v>
@@ -3699,33 +3801,33 @@
         <v>10</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>60</v>
+        <v>102</v>
       </c>
       <c r="K42" s="3">
-        <v>39</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>25</v>
@@ -3734,33 +3836,33 @@
         <v>10</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>224</v>
+        <v>191</v>
       </c>
       <c r="K43" s="3">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>244</v>
+        <v>134</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>245</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>246</v>
+        <v>80</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>25</v>
@@ -3769,33 +3871,33 @@
         <v>10</v>
       </c>
       <c r="F44" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="J44" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>112</v>
-      </c>
       <c r="K44" s="3">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="B45" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="C45" s="3" t="s">
         <v>250</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>25</v>
@@ -3804,138 +3906,138 @@
         <v>10</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>127</v>
+        <v>253</v>
       </c>
       <c r="K45" s="3">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>192</v>
+        <v>255</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>74</v>
+        <v>256</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E46" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>232</v>
+        <v>102</v>
       </c>
       <c r="K46" s="3">
-        <v>24</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>255</v>
+        <v>97</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>124</v>
+        <v>80</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E47" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>259</v>
+        <v>60</v>
       </c>
       <c r="K47" s="3">
-        <v>11</v>
+        <v>40</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>211</v>
+        <v>263</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E48" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>97</v>
+        <v>49</v>
       </c>
       <c r="K48" s="3">
-        <v>0</v>
+        <v>39</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>74</v>
+        <v>136</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>25</v>
@@ -3944,30 +4046,30 @@
         <v>6</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>266</v>
+        <v>60</v>
       </c>
       <c r="K49" s="3">
-        <v>17</v>
+        <v>40</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>74</v>
@@ -3979,33 +4081,33 @@
         <v>6</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>253</v>
+        <v>271</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>97</v>
+        <v>273</v>
       </c>
       <c r="K50" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>74</v>
+        <v>275</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>25</v>
@@ -4014,339 +4116,656 @@
         <v>6</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>253</v>
+        <v>276</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>127</v>
+        <v>162</v>
       </c>
       <c r="K51" s="3">
-        <v>1</v>
+        <v>33</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>272</v>
+        <v>134</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>274</v>
+        <v>74</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E52" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="K52" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>278</v>
+        <v>243</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>187</v>
+        <v>74</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E53" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H53" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="K53" s="3">
-        <v>23</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>283</v>
+        <v>270</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>211</v>
+        <v>74</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E54" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F54" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I54" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="G54" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I54" s="3" t="s">
+      <c r="J54" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>286</v>
-      </c>
       <c r="K54" s="3">
-        <v>7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="B55" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="B55" s="3" t="s">
+      <c r="C55" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E55" s="3">
+        <v>6</v>
+      </c>
+      <c r="F55" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="C55" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E55" s="3">
-        <v>3</v>
-      </c>
-      <c r="F55" s="3" t="s">
+      <c r="G55" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I55" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="G55" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H55" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I55" s="3" t="s">
-        <v>290</v>
-      </c>
       <c r="J55" s="3" t="s">
-        <v>97</v>
+        <v>253</v>
       </c>
       <c r="K55" s="3">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="B56" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="B56" s="3" t="s">
+      <c r="C56" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E56" s="3">
+        <v>6</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I56" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="C56" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E56" s="3">
-        <v>3</v>
-      </c>
-      <c r="F56" s="3" t="s">
+      <c r="J56" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="G56" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H56" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I56" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="J56" s="3" t="s">
-        <v>295</v>
-      </c>
       <c r="K56" s="3">
-        <v>37</v>
+        <v>12</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>260</v>
+        <v>97</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>156</v>
+        <v>80</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E57" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>289</v>
+        <v>267</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>77</v>
+        <v>191</v>
       </c>
       <c r="K57" s="3">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>298</v>
+        <v>149</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>300</v>
+        <v>256</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E58" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>289</v>
+        <v>267</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>66</v>
+        <v>282</v>
       </c>
       <c r="K58" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>302</v>
+        <v>67</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="C59" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E59" s="3">
+        <v>6</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I59" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E59" s="3">
-        <v>3</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>304</v>
-      </c>
       <c r="J59" s="3" t="s">
-        <v>83</v>
+        <v>119</v>
       </c>
       <c r="K59" s="3">
-        <v>4</v>
+        <v>19</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E60" s="3">
+        <v>6</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="K60" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="B61" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="B60" s="3" t="s">
+      <c r="C61" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="C60" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="D60" s="3" t="s">
+      <c r="D61" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E60" s="3">
-        <v>0</v>
-      </c>
-      <c r="F60" s="3"/>
-      <c r="G60" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I60" s="3" t="s">
+      <c r="E61" s="3">
+        <v>4</v>
+      </c>
+      <c r="F61" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="K60" s="3">
+      <c r="G61" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I61" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="J61" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="K61" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E62" s="3">
+        <v>4</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="K62" s="3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E63" s="3">
+        <v>4</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I63" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="J63" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="K63" s="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E64" s="3">
         <v>3</v>
       </c>
+      <c r="F64" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I64" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="J64" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="K64" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E65" s="3">
+        <v>3</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I65" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="J65" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="K65" s="3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E66" s="3">
+        <v>3</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="K66" s="3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E67" s="3">
+        <v>3</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I67" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="J67" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="K67" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E68" s="3">
+        <v>3</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I68" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="J68" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="K68" s="3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E69" s="3">
+        <v>3</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I69" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="J69" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="K69" s="3">
+        <v>3</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K60"/>
+  <autoFilter ref="A1:K69"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -4407,6 +4826,15 @@
     <hyperlink ref="I58" r:id="rId57"/>
     <hyperlink ref="I59" r:id="rId58"/>
     <hyperlink ref="I60" r:id="rId59"/>
+    <hyperlink ref="I61" r:id="rId60"/>
+    <hyperlink ref="I62" r:id="rId61"/>
+    <hyperlink ref="I63" r:id="rId62"/>
+    <hyperlink ref="I64" r:id="rId63"/>
+    <hyperlink ref="I65" r:id="rId64"/>
+    <hyperlink ref="I66" r:id="rId65"/>
+    <hyperlink ref="I67" r:id="rId66"/>
+    <hyperlink ref="I68" r:id="rId67"/>
+    <hyperlink ref="I69" r:id="rId68"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4414,11 +4842,11 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="47" customWidth="1"/>
+    <col min="1" max="1" width="29" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="25" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="60" customWidth="1"/>
+    <col min="5" max="5" width="59" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
@@ -4437,10 +4865,10 @@
         <v>39</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>43</v>
@@ -4448,199 +4876,103 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>92</v>
+        <v>187</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>93</v>
+        <v>188</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D2" s="3">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>95</v>
+        <v>189</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>96</v>
+        <v>190</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>97</v>
+        <v>191</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>103</v>
+        <v>204</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>104</v>
+        <v>205</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D3" s="3">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>106</v>
+        <v>206</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>107</v>
+        <v>207</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>97</v>
+        <v>191</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>209</v>
+        <v>242</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>210</v>
+        <v>243</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D4" s="3">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>212</v>
+        <v>240</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>213</v>
+        <v>244</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>97</v>
+        <v>191</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>217</v>
+        <v>97</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>192</v>
+        <v>294</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D5" s="3">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>218</v>
+        <v>267</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>219</v>
+        <v>295</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" s="3">
-        <v>6</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" s="3">
-        <v>6</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" s="3">
-        <v>4</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" s="3">
-        <v>3</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>97</v>
+        <v>191</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G9"/>
+  <autoFilter ref="A1:G5"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
     <hyperlink ref="F4" r:id="rId3"/>
     <hyperlink ref="F5" r:id="rId4"/>
-    <hyperlink ref="F6" r:id="rId5"/>
-    <hyperlink ref="F7" r:id="rId6"/>
-    <hyperlink ref="F8" r:id="rId7"/>
-    <hyperlink ref="F9" r:id="rId8"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4655,178 +4987,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>308</v>
+        <v>342</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>309</v>
+        <v>343</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>310</v>
+        <v>344</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>289</v>
+        <v>322</v>
       </c>
       <c r="B2" s="3">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>311</v>
+        <v>345</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>284</v>
+        <v>316</v>
       </c>
       <c r="B3" s="3">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>312</v>
+        <v>346</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>247</v>
+        <v>332</v>
       </c>
       <c r="B4" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>313</v>
+        <v>347</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>314</v>
+        <v>348</v>
       </c>
       <c r="B5" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>315</v>
+        <v>349</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>279</v>
+        <v>307</v>
       </c>
       <c r="B6" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>316</v>
+        <v>350</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>275</v>
+        <v>311</v>
       </c>
       <c r="B7" s="3">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>317</v>
+        <v>351</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="B8" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>318</v>
+        <v>352</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>319</v>
+        <v>219</v>
       </c>
       <c r="B9" s="3">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>320</v>
+        <v>353</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>321</v>
+        <v>354</v>
       </c>
       <c r="B10" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>322</v>
+        <v>355</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>323</v>
+        <v>356</v>
       </c>
       <c r="B11" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>324</v>
+        <v>357</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>293</v>
+        <v>358</v>
       </c>
       <c r="B12" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>325</v>
+        <v>359</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>326</v>
+        <v>360</v>
       </c>
       <c r="B13" s="3">
         <v>9</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>327</v>
+        <v>361</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>328</v>
+        <v>362</v>
       </c>
       <c r="B14" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>329</v>
+        <v>363</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>330</v>
+        <v>364</v>
       </c>
       <c r="B15" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>331</v>
+        <v>365</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>332</v>
+        <v>366</v>
       </c>
       <c r="B16" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>333</v>
+        <v>367</v>
       </c>
     </row>
   </sheetData>
@@ -4846,10 +5178,10 @@
         <v>38</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>334</v>
+        <v>368</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>335</v>
+        <v>369</v>
       </c>
     </row>
     <row r="2">
@@ -4857,10 +5189,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>336</v>
+        <v>370</v>
       </c>
     </row>
     <row r="3">
@@ -4868,10 +5200,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>337</v>
+        <v>371</v>
       </c>
     </row>
     <row r="4">
@@ -4879,10 +5211,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>338</v>
+        <v>372</v>
       </c>
     </row>
     <row r="5">
@@ -4893,7 +5225,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>339</v>
+        <v>373</v>
       </c>
     </row>
     <row r="6">
@@ -4904,7 +5236,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>340</v>
+        <v>374</v>
       </c>
     </row>
   </sheetData>
@@ -4925,13 +5257,13 @@
         <v>41</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>341</v>
+        <v>375</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>342</v>
+        <v>376</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>343</v>
+        <v>377</v>
       </c>
     </row>
     <row r="2">
@@ -4942,7 +5274,7 @@
         <v>5</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>344</v>
+        <v>378</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -4951,10 +5283,10 @@
         <v>31</v>
       </c>
       <c r="B3" s="3">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>344</v>
+        <v>378</v>
       </c>
       <c r="D3" s="3"/>
     </row>
@@ -4963,10 +5295,10 @@
         <v>33</v>
       </c>
       <c r="B4" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>344</v>
+        <v>378</v>
       </c>
       <c r="D4" s="3"/>
     </row>
